--- a/config/xlsx/recipes.xlsx
+++ b/config/xlsx/recipes.xlsx
@@ -500,7 +500,7 @@
         <v>31</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>

--- a/config/xlsx/recipes.xlsx
+++ b/config/xlsx/recipes.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:E211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -447,7 +447,6 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,394 +475,4415 @@
           <t>craft_time</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>crafting_level</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>炼筑基丹</t>
+          <t>养气散</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>101;102</t>
+          <t>5001;9001</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>31</v>
+        <v>27001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>炼金丹丹</t>
+          <t>引气丸</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>103;104</t>
+          <t>5002;9002</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>32</v>
+        <v>27002</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>炼元婴丹</t>
+          <t>固元粉</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>105;106</t>
+          <t>5003;1001</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33</v>
+        <v>27003</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>炼化神丹</t>
+          <t>培元丹</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>107;108</t>
+          <t>5004;1002;9003</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>34</v>
+        <v>27004</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>炼合体丹</t>
+          <t>灵髓丸</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>109;110</t>
+          <t>5005;1003;9004</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>35</v>
+        <v>27005</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>炼大乘丹</t>
+          <t>黄芽丹</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>111;112</t>
+          <t>1004;6004</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>36</v>
+        <v>27006</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>炼渡劫丹</t>
+          <t>小还丹</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>113;114</t>
+          <t>1005;6005;9005;3001</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>37</v>
+        <v>27007</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>炼聚气散</t>
+          <t>赤阳丸</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1006;6006;12006;3002</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>71</v>
+        <v>27008</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>炼培元散</t>
+          <t>青冥丹</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1007;6007;9007;3003</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>72</v>
+        <v>27009</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>炼凝神散</t>
+          <t>玄金散</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>1008;6008;9008</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>73</v>
+        <v>27010</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>炼增元散</t>
+          <t>冰魄丹</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>1009;7005;8005;3005</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>74</v>
+        <v>27011</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>炼圣药</t>
+          <t>火灵丸</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>125;126</t>
+          <t>1010;7006;8006;3006</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>74</v>
+        <v>27012</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>炼铜锭</t>
+          <t>青玄丹</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>1011;7007;8007;3007</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>65</v>
+        <v>27013</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>炼铁锭</t>
+          <t>五雷丹</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1012;7008;8008;3008</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>66</v>
+        <v>27014</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>炼银锭</t>
+          <t>地龙丹</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>7009;8009;3009;6009</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>67</v>
+        <v>27015</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>星狼丹</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>7010;8010;3010;6010</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>27016</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>紫狐丹</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>7011;8011;3011;6011</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>27017</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>炼金锭</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>九命丹</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>7012;8012;9012;6012</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>27018</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>地皇丹</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>5009;5012;12009</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>27019</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>星芒丹</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>5010;5011;9010</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>27020</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>紫府金丹</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>5011;9011;1010</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>27021</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>九窍还魂丹</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>5012;9012;1012</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>27022</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>麒麟丹</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>7013;8013;12013</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>27023</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>真龙丹</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>7014;8014;12014</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>27024</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>凤凰丹</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>7015;8015;9015</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>27025</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>混沌丹</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>7016;8016;9016</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>27026</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>涅槃丹</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>5013;6013;3013</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>27027</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>龙牙丹</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>5014;6014;3014</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>27028</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>凤羽金丹</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>5015;6015;3015</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>27029</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>混沌玄丹</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>5016;6016;3016</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>27030</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>筑基丹</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>22004;22004</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>27031</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>聚灵大丹</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>22002;9004</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>27081</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>培元大丹</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>22003;6004;5004</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>27033</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>玄冰大丹</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>22005;6005;3005</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>27034</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>赤阳大丹</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>22006;6006;3006</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>27035</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>青木大丹</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>22007;6007;3007</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>27036</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>雷音大丹</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>22008;6008;3008</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>27037</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>地脉大丹</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>22009;6009;3009</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>27038</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>星辉大丹</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>22010;6010;3010</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>27039</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>紫府大丹</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>22011;6011;3011</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>27040</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>九窍大丹</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>22012;6012;9012</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>27041</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>涅槃大丹</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>22013;6013;3013</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>27042</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>龙灵大丹</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>22014;6014;3014</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>27043</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>凤血大丹</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>22015;6015;3015</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>27044</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>混沌大丹</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>22016;6016;3016</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>27045</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>九转金丹</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>22011;22012;22013;3016</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>27046</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>太清仙丹</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>22014;22015;22016;4016</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>27047</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>天地玄黄丹</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>27006;27034;27019;27030</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>27048</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>五气朝元丹</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>27013;27035;27038;27039</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>27049</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>万法归宗丹</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>27045;27047;27046;9016</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>27050</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>回灵散</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>9001;3001</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>27051</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>复灵丸</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>9002;3002</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>27052</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>清心露</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>9003;3003</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>27053</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>玉灵丹</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>9004;3004;6002</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>27054</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>冰心丸</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>9005;3005;6005</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>27055</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>火灵散</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>12006;3006;6006</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>27056</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>青木露</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>9007;3007;6007</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>27057</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>雷光液</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>9008;3008;6008</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>27058</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>地脉浆</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>12009;3009;6009</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>27059</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>星辉液</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>9010;3010;6010</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>27060</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>寒泉丹</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>1005;7005;8005;6005</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>27061</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>炎泉丹</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>1006;7006;8006;6006</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>27062</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>青泉丹</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>1007;7007;8007;6007</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>27063</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>雷泉丹</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>1008;7008;8008;6008</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>27064</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>地髓大丹</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>1009;7009;8009;6009</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>27065</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>星尘大丹</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>1010;7010;8010;6010</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>27066</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>紫气大丹</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>1011;7011;8011;6011</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>27067</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>1</v>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>九泉大丹</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>1012;7012;8012;6012</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>27068</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>地皇灵丹</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>5009;12009</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>27069</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>星芒灵丹</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>5010;9010</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>27070</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>紫府灵丹</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>5011;9011</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>27071</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>九窍灵丹</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>5012;9012</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>27072</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>麒麟灵丹</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>7013;8013;12013</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>27073</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>龙鳞灵丹</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>7014;8014;12014</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>27074</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>凤羽灵丹</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>7015;8015;9015</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>27075</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>混沌灵丹</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>7016;8016;9016</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>27080</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>涅槃灵丹</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>5013;6013;3013</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>27077</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>龙息灵丹</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>5014;6014;3014</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>27078</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>凤血灵丹</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>5015;6015;3015</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>27079</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>混沌灵丹</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>5016;6016;3016</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>27080</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>聚灵大丹</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>22002;3002</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>27081</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>玉液大丹</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>22004;9004;3004</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>27082</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>玄冰大灵丹</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>22005;3005;6005</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>27083</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>赤阳大灵丹</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>22006;3006;6006</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>27084</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>青木大灵丹</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>22007;3007;6007</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>27085</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>雷音大灵丹</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>22008;3008;6008</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>27086</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>地脉大灵丹</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>22009;3009;6009</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>27087</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>星辉大灵丹</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>22010;3010;6010</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>27088</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>紫府大灵丹</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>22011;3011;6011</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>27089</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>九窍大灵丹</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>22012;9012;6012</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>27090</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>涅槃大灵丹</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>22013;3013;6013</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>27091</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>龙灵大灵丹</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>22014;3014;6014</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>27092</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>凤血大灵丹</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>22015;3015;6015</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>27093</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>混沌大灵丹</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>22016;3016;6016</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>27094</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>九转还灵丹</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>27082;27087;27090</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>27095</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>太清还灵丹</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>27092;27093;27094</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>27096</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>五灵归元丹</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>27085;27084;27087;27088</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>27097</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>万灵朝宗丹</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>27073;27074;27075;27076</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>27098</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>灵气源泉丹</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>10010;10012;10014;10016</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>27099</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>生生不息丹</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>27051;27054;27068;27080</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>27100</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>黄粱米酒</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>5001;9001</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>27101</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>清溪果酿</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>6002;9002</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>27102</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>百花醉</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>3002;9003</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>27103</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>玉露琼浆</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>9004;6004</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>27104</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>青芽酿</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>5003;3003;6003</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>27105</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>霜华酿</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>5005;3005;6005</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>27106</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>赤阳烧</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>5006;3006;6006</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>27107</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>青玄酿</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>5007;3007;6007</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>27108</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>雷火酒</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>5008;3008;6008</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>27109</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>地脉醇</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>5009;3009;6009</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>27110</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>星芒醉</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>5010;3010;6010</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>27111</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>紫府仙酿</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>5011;3011;6011</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>27112</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>九孔玉液酒</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>5012;9012;6012</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>27113</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>涅槃重生酿</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>5013;3013;6013</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>27114</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>龙息醇</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>5014;3014;6014</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>27115</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>凤羽天酿</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>5015;3015;6015</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>27116</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>混沌元酒</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>5016;3016;6016</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>27117</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>冰蚕寒酿</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>7005;3005;1005</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>27118</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>火浣烈酒</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>7006;3006;1006</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>27119</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>龟甲养身酒</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>7007;3007;1007</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>27120</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>雷蟒电光酒</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>7008;3008;1008</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>27121</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>地龙沉酿</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>7009;3009;1009</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>27122</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>星貂幻酒</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>7010;3010;1010</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>27123</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>紫狐迷魂酒</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>7011;3011;1011</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>27124</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>九尾灵酒</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>7012;9012;1012</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>27125</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>麒麟祥瑞酒</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>7013;12013;8013</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>27126</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>龙鳞战酒</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>7014;12014;8014</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>27127</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>凤羽涅槃酒</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>7015;9015;8015</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>27128</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>混沌悟道酒</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>7016;9016;8016</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>27129</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>灵果甘酿</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>6004;9004;3004</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>27130</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>地脉灵根酒</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>6009;12009;3009</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>27131</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>星辉甘霖酒</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>6010;9010;3010</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>27132</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>紫光仙酒</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>6011;9011;3011</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>27133</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>九窍玉髓酒</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>6012;9012;5012</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>27134</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>涅槃烈酒</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>6013;12013;3013</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>27135</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>龙涎封侯酒</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>6014;12014;3014</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>27136</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>凤羽飞天酒</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>6015;9015;3015</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>27137</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>混沌朝圣酒</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>6016;9016;3016</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>27138</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>寒泉冻骨酒</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>9005;1005;3005</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>27139</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>炎泉沸血酒</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>12006;1006;3006</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>27140</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>青泉生机酒</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>9007;1007;3007</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>27141</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>雷泉电身酒</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>9008;1008;3008</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>27142</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>九转回春酒</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>27051;27054;27068</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>27143</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>百草灵酒</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>1001;1002;1003;9004</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>27144</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>五灵合酿酒</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>27108;27107;27110;27111</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>27145</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>三花聚顶酒</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>3002;3007;3011</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>27146</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>五行调和酒</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>27118;27119;27120;27121</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>27147</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>九龙升天酒</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>27115;27127;27136;5014</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>27148</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>九凤朝凰酒</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>27116;27128;27137;5015</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>27149</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>混沌万道酒</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>27117;27129;27138;5016</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>27150</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>铁木剑</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>2002;9001</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>28001</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>铜锋剑</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>2003;9002;4001</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>28002</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>银光剑</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>2003;2004;4003;9003</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>28003</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>玄金短剑</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>2004;4004;9004</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>28004</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>寒渊冰剑</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>2005;4005;9005;4002</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>28005</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>赤炎火剑</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>2006;4006;9006</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>28006</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>青灵木剑</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>2007;4007;9007;3007</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>28007</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>金雷斩邪剑</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>2008;4008;9008;3008</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>28008</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>地脉重剑</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>2009;4009;9009;3009</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>28009</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>星陨长剑</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>2010;4010;27060;3010</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>28010</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>虚空影剑</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>2011;4011;9011;3011</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>28011</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>九幽玄冥剑</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>2012;4012;9012;6012</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>28012</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>太阳真光剑</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>2013;4013;9013;3013</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>28013</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>太阴寒月剑</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>2014;4014;9014;3014</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>28014</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>星河无极剑</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>2015;4015;9015;3015</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>28015</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙开天剑</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>2016;4016;9016;3016</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>28016</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>清风阵</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>13101;7001;9001</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>28017</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>聚灵阵</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>13102;7002;9002;4001</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>28018</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>铁壁阵</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>13103;7003;4002;9003</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>28019</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>三才锁灵阵</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>13104;7004;4004;9004</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>28020</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>四象寒冰阵</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>13105;7005;4005;3005</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>28021</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>烈焰困阵</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>13106;7006;4006;3006</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>28022</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>厚土御阵</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>13107;7007;4007;3007</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>28023</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>五雷诛邪阵</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>13108;7008;4008;3008</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>28024</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>地脉龙吟阵</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>13109;7009;4009;3009</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>28025</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>星罗迷阵</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>13110;7010;4010;3010</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>28026</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>九幻迷心阵</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>13111;7011;4011;3011</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>28027</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>九命续生阵</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>13112;7012;4012;9012</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>28028</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>瑞兽祥云阵</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>13113;7013;4013;3013</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>28029</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>真龙御天阵</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>13114;7014;4014;3014</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>28030</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>凤舞涅槃阵</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>13115;7015;4015;3015</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>28031</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>混沌归一阵</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>13116;7016;4016;3016</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>28032</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>驱兽符</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>7001;8001;9001</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>28033</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>避尘符</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>7002;8002;9001</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>28034</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>火弹符</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>7003;8003;9002;3002</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>28035</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>金甲符</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>7004;8004;9002;3004</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>28036</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>冰锥符</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>7005;8005;9003;3005</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>28037</v>
+      </c>
+      <c r="E188" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>炎爆符</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>7006;8006;9003;3006</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>28038</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>青藤符</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>7007;8007;9004;3007</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>28039</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>五雷符</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>7008;8008;9004;3008</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>28040</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>地裂符</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>7009;8009;9005;3009</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>28041</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>星遁符</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>7010;8010;9005;3010</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>28042</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>幻身符</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>7011;8011;9006;3011</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>28043</v>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>续命符</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>7012;8012;9006;9012</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>28044</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>祥瑞符</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>7013;8013;9007;3013</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>28045</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>龙威符</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>7014;8014;9007;3014</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>28046</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>涅槃符</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>7015;8015;9008;3015</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>28047</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>混沌符</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>7016;8016;9008;3016</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>28048</v>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>引气筑基散</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1002, 'count': 3};{'id': 5002, 'count': 5};{'id': 9002, 'count': 3}</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>28049</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>凝元破境丹</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1003, 'count': 4};{'id': 5004, 'count': 3};{'id': 9004, 'count': 2};{'id': 3004, 'count': 2}</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>28050</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>筑基破障丹</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1004, 'count': 4};{'id': 1005, 'count': 2};{'id': 27004, 'count': 1};{'id': 4004, 'count': 3}</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>28051</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>固基培元丹</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1005, 'count': 3};{'id': 1006, 'count': 2};{'id': 9006, 'count': 3};{'id': 4006, 'count': 2}</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>28052</v>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>通玄化灵丹</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1007, 'count': 3};{'id': 1008, 'count': 2};{'id': 9008, 'count': 3};{'id': 4008, 'count': 2}</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>28053</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>金丹破障丹</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1009, 'count': 3};{'id': 1010, 'count': 2};{'id': 27007, 'count': 1};{'id': 4009, 'count': 3}</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>28054</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>凝丹化形丹</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1009, 'count': 3};{'id': 1011, 'count': 2};{'id': 9011, 'count': 3};{'id': 4011, 'count': 2}</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>28055</v>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>九转金丹</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1012, 'count': 3};{'id': 1011, 'count': 2};{'id': 9012, 'count': 3};{'id': 4012, 'count': 2}</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>28056</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>元婴破障丹</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 1012, 'count': 4};{'id': 2009, 'count': 3};{'id': 27009, 'count': 1};{'id': 8012, 'count': 3}</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>28057</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>元婴凝神丹</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 7013, 'count': 2};{'id': 7014, 'count': 2};{'id': 9013, 'count': 3};{'id': 4013, 'count': 2}</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>28058</v>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>元婴归元丹</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 7015, 'count': 2};{'id': 7014, 'count': 2};{'id': 9015, 'count': 3};{'id': 4014, 'count': 2}</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>28059</v>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>化神渡劫丹</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>{'id': 7016, 'count': 2};{'id': 8016, 'count': 2};{'id': 3016, 'count': 3};{'id': 4016, 'count': 2}</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>28060</v>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/config/xlsx/recipes.xlsx
+++ b/config/xlsx/recipes.xlsx
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'count': 3};{'id': 5002, 'count': 5};{'id': 9002, 'count': 3}</t>
+          <t>1002;5002;9002</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'count': 4};{'id': 5004, 'count': 3};{'id': 9004, 'count': 2};{'id': 3004, 'count': 2}</t>
+          <t>1003;5004;9004;3004</t>
         </is>
       </c>
       <c r="D201" s="3" t="n">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1004, 'count': 4};{'id': 1005, 'count': 2};{'id': 27004, 'count': 1};{'id': 4004, 'count': 3}</t>
+          <t>1004;1005;27004;4004</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1005, 'count': 3};{'id': 1006, 'count': 2};{'id': 9006, 'count': 3};{'id': 4006, 'count': 2}</t>
+          <t>1005;1006;9006;4006</t>
         </is>
       </c>
       <c r="D203" s="3" t="n">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1007, 'count': 3};{'id': 1008, 'count': 2};{'id': 9008, 'count': 3};{'id': 4008, 'count': 2}</t>
+          <t>1007;1008;9008;4008</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1009, 'count': 3};{'id': 1010, 'count': 2};{'id': 27007, 'count': 1};{'id': 4009, 'count': 3}</t>
+          <t>1009;1010;27007;4009</t>
         </is>
       </c>
       <c r="D205" s="3" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1009, 'count': 3};{'id': 1011, 'count': 2};{'id': 9011, 'count': 3};{'id': 4011, 'count': 2}</t>
+          <t>1009;1011;9011;4011</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1012, 'count': 3};{'id': 1011, 'count': 2};{'id': 9012, 'count': 3};{'id': 4012, 'count': 2}</t>
+          <t>1012;1011;9012;4012</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>{'id': 1012, 'count': 4};{'id': 2009, 'count': 3};{'id': 27009, 'count': 1};{'id': 8012, 'count': 3}</t>
+          <t>1012;2009;27009;8012</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>{'id': 7013, 'count': 2};{'id': 7014, 'count': 2};{'id': 9013, 'count': 3};{'id': 4013, 'count': 2}</t>
+          <t>7013;7014;9013;4013</t>
         </is>
       </c>
       <c r="D209" s="3" t="n">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>{'id': 7015, 'count': 2};{'id': 7014, 'count': 2};{'id': 9015, 'count': 3};{'id': 4014, 'count': 2}</t>
+          <t>7015;7014;9015;4014</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>{'id': 7016, 'count': 2};{'id': 8016, 'count': 2};{'id': 3016, 'count': 3};{'id': 4016, 'count': 2}</t>
+          <t>7016;8016;3016;4016</t>
         </is>
       </c>
       <c r="D211" s="3" t="n">

--- a/config/xlsx/recipes.xlsx
+++ b/config/xlsx/recipes.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>22004;22004</t>
+          <t>27004;27004</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>22002;9004</t>
+          <t>27002;9004</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>22003;6004;5004</t>
+          <t>27003;6004;5004</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>22005;6005;3005</t>
+          <t>27005;6005;3005</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>22006;6006;3006</t>
+          <t>27008;6006;3006</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>22007;6007;3007</t>
+          <t>27009;6007;3007</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>22008;6008;3008</t>
+          <t>27010;6008;3008</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>22009;6009;3009</t>
+          <t>27011;6009;3009</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>22010;6010;3010</t>
+          <t>27012;6010;3010</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>22011;6011;3011</t>
+          <t>27013;6011;3011</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>22012;6012;9012</t>
+          <t>27014;6012;9012</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>22013;6013;3013</t>
+          <t>27023;6013;3013</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>22014;6014;3014</t>
+          <t>27024;6014;3014</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>22015;6015;3015</t>
+          <t>27025;6015;3015</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>22016;6016;3016</t>
+          <t>27026;6016;3016</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>22011;22012;22013;3016</t>
+          <t>27013;27014;27023;3016</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>22014;22015;22016;4016</t>
+          <t>27024;27025;27026;4016</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>22002;3002</t>
+          <t>27002;3002</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>22004;9004;3004</t>
+          <t>27004;9004;3004</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>22005;3005;6005</t>
+          <t>27005;3005;6005</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>22006;3006;6006</t>
+          <t>27008;3006;6006</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>22007;3007;6007</t>
+          <t>27009;3007;6007</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>22008;3008;6008</t>
+          <t>27010;3008;6008</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>22009;3009;6009</t>
+          <t>27011;3009;6009</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>22010;3010;6010</t>
+          <t>27012;3010;6010</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>22011;3011;6011</t>
+          <t>27013;3011;6011</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>22012;9012;6012</t>
+          <t>27014;9012;6012</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>22013;3013;6013</t>
+          <t>27023;3013;6013</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>22014;3014;6014</t>
+          <t>27024;3014;6014</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>22015;3015;6015</t>
+          <t>27025;3015;6015</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>22016;3016;6016</t>
+          <t>27026;3016;6016</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
@@ -2515,20 +2515,20 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>万灵朝宗丹</t>
+          <t>灵气源泉丹</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>27073;27074;27075;27076</t>
+          <t>10010;10012;10014;10016</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>27098</v>
+        <v>27099</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>25</v>
@@ -2536,20 +2536,20 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>灵气源泉丹</t>
+          <t>生生不息丹</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>10010;10012;10014;10016</t>
+          <t>27051;27054;27068;27080</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>27099</v>
+        <v>27100</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>25</v>
@@ -2557,41 +2557,41 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>生生不息丹</t>
+          <t>黄粱米酒</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>27051;27054;27068;27080</t>
+          <t>5001;9001</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>27100</v>
+        <v>27101</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>黄粱米酒</t>
+          <t>清溪果酿</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>5001;9001</t>
+          <t>6002;9002</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>27101</v>
+        <v>27102</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>15</v>
@@ -2599,20 +2599,20 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>清溪果酿</t>
+          <t>百花醉</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>6002;9002</t>
+          <t>3002;9003</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>27102</v>
+        <v>27103</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>15</v>
@@ -2620,20 +2620,20 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>百花醉</t>
+          <t>玉露琼浆</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>3002;9003</t>
+          <t>9004;6004</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>27103</v>
+        <v>27104</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>15</v>
@@ -2641,41 +2641,41 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>玉露琼浆</t>
+          <t>青芽酿</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>9004;6004</t>
+          <t>5003;3003;6003</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>27104</v>
+        <v>27105</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>青芽酿</t>
+          <t>霜华酿</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>5003;3003;6003</t>
+          <t>5005;3005;6005</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>27105</v>
+        <v>27106</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>20</v>
@@ -2683,20 +2683,20 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>霜华酿</t>
+          <t>赤阳烧</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>5005;3005;6005</t>
+          <t>5006;3006;6006</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>27106</v>
+        <v>27107</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>20</v>
@@ -2704,20 +2704,20 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>赤阳烧</t>
+          <t>青玄酿</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>5006;3006;6006</t>
+          <t>5007;3007;6007</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>27107</v>
+        <v>27108</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>20</v>
@@ -2725,20 +2725,20 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>青玄酿</t>
+          <t>雷火酒</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>5007;3007;6007</t>
+          <t>5008;3008;6008</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>27108</v>
+        <v>27109</v>
       </c>
       <c r="E109" s="3" t="n">
         <v>20</v>
@@ -2746,20 +2746,20 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>雷火酒</t>
+          <t>地脉醇</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>5008;3008;6008</t>
+          <t>5009;3009;6009</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>27109</v>
+        <v>27110</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>20</v>
@@ -2767,20 +2767,20 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>地脉醇</t>
+          <t>星芒醉</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>5009;3009;6009</t>
+          <t>5010;3010;6010</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>27110</v>
+        <v>27111</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>20</v>
@@ -2788,20 +2788,20 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>星芒醉</t>
+          <t>紫府仙酿</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>5010;3010;6010</t>
+          <t>5011;3011;6011</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>27111</v>
+        <v>27112</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>20</v>
@@ -2809,20 +2809,20 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>紫府仙酿</t>
+          <t>九孔玉液酒</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>5011;3011;6011</t>
+          <t>5012;9012;6012</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>27112</v>
+        <v>27113</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>20</v>
@@ -2830,20 +2830,20 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>九孔玉液酒</t>
+          <t>涅槃重生酿</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>5012;9012;6012</t>
+          <t>5013;3013;6013</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>27113</v>
+        <v>27114</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>20</v>
@@ -2851,20 +2851,20 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>涅槃重生酿</t>
+          <t>龙息醇</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>5013;3013;6013</t>
+          <t>5014;3014;6014</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>27114</v>
+        <v>27115</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>20</v>
@@ -2872,20 +2872,20 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>龙息醇</t>
+          <t>凤羽天酿</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>5014;3014;6014</t>
+          <t>5015;3015;6015</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>27115</v>
+        <v>27116</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>20</v>
@@ -2893,20 +2893,20 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>凤羽天酿</t>
+          <t>混沌元酒</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>5015;3015;6015</t>
+          <t>5016;3016;6016</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>27116</v>
+        <v>27117</v>
       </c>
       <c r="E117" s="3" t="n">
         <v>20</v>
@@ -2914,20 +2914,20 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>混沌元酒</t>
+          <t>冰蚕寒酿</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>5016;3016;6016</t>
+          <t>7005;3005;1005</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>27117</v>
+        <v>27118</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>20</v>
@@ -2935,20 +2935,20 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>冰蚕寒酿</t>
+          <t>火浣烈酒</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>7005;3005;1005</t>
+          <t>7006;3006;1006</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>27118</v>
+        <v>27119</v>
       </c>
       <c r="E119" s="3" t="n">
         <v>20</v>
@@ -2956,20 +2956,20 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>火浣烈酒</t>
+          <t>龟甲养身酒</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>7006;3006;1006</t>
+          <t>7007;3007;1007</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>27119</v>
+        <v>27120</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>20</v>
@@ -2977,20 +2977,20 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>龟甲养身酒</t>
+          <t>雷蟒电光酒</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>7007;3007;1007</t>
+          <t>7008;3008;1008</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>27120</v>
+        <v>27121</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>20</v>
@@ -2998,20 +2998,20 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>雷蟒电光酒</t>
+          <t>地龙沉酿</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>7008;3008;1008</t>
+          <t>7009;3009;1009</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>27121</v>
+        <v>27122</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>20</v>
@@ -3019,20 +3019,20 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>地龙沉酿</t>
+          <t>星貂幻酒</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>7009;3009;1009</t>
+          <t>7010;3010;1010</t>
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>27122</v>
+        <v>27123</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>20</v>
@@ -3040,20 +3040,20 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>星貂幻酒</t>
+          <t>紫狐迷魂酒</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>7010;3010;1010</t>
+          <t>7011;3011;1011</t>
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>27123</v>
+        <v>27124</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>20</v>
@@ -3061,20 +3061,20 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>紫狐迷魂酒</t>
+          <t>九尾灵酒</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>7011;3011;1011</t>
+          <t>7012;9012;1012</t>
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>27124</v>
+        <v>27125</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>20</v>
@@ -3082,20 +3082,20 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>九尾灵酒</t>
+          <t>麒麟祥瑞酒</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>7012;9012;1012</t>
+          <t>7013;12013;8013</t>
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>27125</v>
+        <v>27126</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>20</v>
@@ -3103,20 +3103,20 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>麒麟祥瑞酒</t>
+          <t>龙鳞战酒</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>7013;12013;8013</t>
+          <t>7014;12014;8014</t>
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>27126</v>
+        <v>27127</v>
       </c>
       <c r="E127" s="3" t="n">
         <v>20</v>
@@ -3124,20 +3124,20 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>龙鳞战酒</t>
+          <t>凤羽涅槃酒</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>7014;12014;8014</t>
+          <t>7015;9015;8015</t>
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>27127</v>
+        <v>27128</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>20</v>
@@ -3145,20 +3145,20 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>凤羽涅槃酒</t>
+          <t>混沌悟道酒</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>7015;9015;8015</t>
+          <t>7016;9016;8016</t>
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>27128</v>
+        <v>27129</v>
       </c>
       <c r="E129" s="3" t="n">
         <v>20</v>
@@ -3166,20 +3166,20 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>混沌悟道酒</t>
+          <t>灵果甘酿</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>7016;9016;8016</t>
+          <t>6004;9004;3004</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>27129</v>
+        <v>27130</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>20</v>
@@ -3187,20 +3187,20 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>灵果甘酿</t>
+          <t>地脉灵根酒</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>6004;9004;3004</t>
+          <t>6009;12009;3009</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>27130</v>
+        <v>27131</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>20</v>
@@ -3208,20 +3208,20 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>地脉灵根酒</t>
+          <t>星辉甘霖酒</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>6009;12009;3009</t>
+          <t>6010;9010;3010</t>
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>27131</v>
+        <v>27132</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>20</v>
@@ -3229,20 +3229,20 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>星辉甘霖酒</t>
+          <t>紫光仙酒</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>6010;9010;3010</t>
+          <t>6011;9011;3011</t>
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>27132</v>
+        <v>27133</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>20</v>
@@ -3250,20 +3250,20 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>紫光仙酒</t>
+          <t>九窍玉髓酒</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>6011;9011;3011</t>
+          <t>6012;9012;5012</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>27133</v>
+        <v>27134</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>20</v>
@@ -3271,20 +3271,20 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>九窍玉髓酒</t>
+          <t>涅槃烈酒</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>6012;9012;5012</t>
+          <t>6013;12013;3013</t>
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>27134</v>
+        <v>27135</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>20</v>
@@ -3292,20 +3292,20 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>涅槃烈酒</t>
+          <t>龙涎封侯酒</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>6013;12013;3013</t>
+          <t>6014;12014;3014</t>
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>27135</v>
+        <v>27136</v>
       </c>
       <c r="E136" s="3" t="n">
         <v>20</v>
@@ -3313,20 +3313,20 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>龙涎封侯酒</t>
+          <t>凤羽飞天酒</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>6014;12014;3014</t>
+          <t>6015;9015;3015</t>
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>27136</v>
+        <v>27137</v>
       </c>
       <c r="E137" s="3" t="n">
         <v>20</v>
@@ -3334,20 +3334,20 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>凤羽飞天酒</t>
+          <t>混沌朝圣酒</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>6015;9015;3015</t>
+          <t>6016;9016;3016</t>
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>27137</v>
+        <v>27138</v>
       </c>
       <c r="E138" s="3" t="n">
         <v>20</v>
@@ -3355,20 +3355,20 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>混沌朝圣酒</t>
+          <t>寒泉冻骨酒</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>6016;9016;3016</t>
+          <t>9005;1005;3005</t>
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>27138</v>
+        <v>27139</v>
       </c>
       <c r="E139" s="3" t="n">
         <v>20</v>
@@ -3376,20 +3376,20 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>寒泉冻骨酒</t>
+          <t>炎泉沸血酒</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>9005;1005;3005</t>
+          <t>12006;1006;3006</t>
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>27139</v>
+        <v>27140</v>
       </c>
       <c r="E140" s="3" t="n">
         <v>20</v>
@@ -3397,20 +3397,20 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>炎泉沸血酒</t>
+          <t>青泉生机酒</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>12006;1006;3006</t>
+          <t>9007;1007;3007</t>
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>27140</v>
+        <v>27141</v>
       </c>
       <c r="E141" s="3" t="n">
         <v>20</v>
@@ -3418,20 +3418,20 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>青泉生机酒</t>
+          <t>雷泉电身酒</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>9007;1007;3007</t>
+          <t>9008;1008;3008</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>27141</v>
+        <v>27142</v>
       </c>
       <c r="E142" s="3" t="n">
         <v>20</v>
@@ -3439,20 +3439,20 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>雷泉电身酒</t>
+          <t>九转回春酒</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>9008;1008;3008</t>
+          <t>27051;27054;27068</t>
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>27142</v>
+        <v>27143</v>
       </c>
       <c r="E143" s="3" t="n">
         <v>20</v>
@@ -3460,41 +3460,41 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>九转回春酒</t>
+          <t>百草灵酒</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>27051;27054;27068</t>
+          <t>1001;1002;1003;9004</t>
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>27143</v>
+        <v>27144</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>百草灵酒</t>
+          <t>五灵合酿酒</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>1001;1002;1003;9004</t>
+          <t>27108;27107;27110;27111</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>27144</v>
+        <v>27145</v>
       </c>
       <c r="E145" s="3" t="n">
         <v>25</v>
@@ -3502,62 +3502,62 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>五灵合酿酒</t>
+          <t>三花聚顶酒</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>27108;27107;27110;27111</t>
+          <t>3002;3007;3011</t>
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>27145</v>
+        <v>27146</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>三花聚顶酒</t>
+          <t>五行调和酒</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>3002;3007;3011</t>
+          <t>27118;27119;27120;27121</t>
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>27146</v>
+        <v>27147</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>五行调和酒</t>
+          <t>九龙升天酒</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>27118;27119;27120;27121</t>
+          <t>27115;27127;27136;5014</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>27147</v>
+        <v>27148</v>
       </c>
       <c r="E148" s="3" t="n">
         <v>25</v>
@@ -3565,20 +3565,20 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>九龙升天酒</t>
+          <t>九凤朝凰酒</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>27115;27127;27136;5014</t>
+          <t>27116;27128;27137;5015</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>27148</v>
+        <v>27149</v>
       </c>
       <c r="E149" s="3" t="n">
         <v>25</v>
@@ -3586,20 +3586,20 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>九凤朝凰酒</t>
+          <t>混沌万道酒</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>27116;27128;27137;5015</t>
+          <t>27117;27129;27138;5016</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>27149</v>
+        <v>27150</v>
       </c>
       <c r="E150" s="3" t="n">
         <v>25</v>
@@ -3607,167 +3607,167 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>混沌万道酒</t>
+          <t>铁木剑</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>27117;27129;27138;5016</t>
+          <t>2002;9001</t>
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>27150</v>
+        <v>28001</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>铁木剑</t>
+          <t>铜锋剑</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>2002;9001</t>
+          <t>2003;9002;4001</t>
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>28001</v>
+        <v>28002</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>铜锋剑</t>
+          <t>银光剑</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>2003;9002;4001</t>
+          <t>2003;2004;4003;9003</t>
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>28002</v>
+        <v>28003</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>银光剑</t>
+          <t>玄金短剑</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>2003;2004;4003;9003</t>
+          <t>2004;4004;9004</t>
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>28003</v>
+        <v>28004</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>玄金短剑</t>
+          <t>寒渊冰剑</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>2004;4004;9004</t>
+          <t>2005;4005;9005;4002</t>
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>28004</v>
+        <v>28005</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>寒渊冰剑</t>
+          <t>赤炎火剑</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>2005;4005;9005;4002</t>
+          <t>2006;4006;9006</t>
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>28005</v>
+        <v>28006</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>赤炎火剑</t>
+          <t>青灵木剑</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>2006;4006;9006</t>
+          <t>2007;4007;9007;3007</t>
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>28006</v>
+        <v>28007</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>青灵木剑</t>
+          <t>金雷斩邪剑</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>2007;4007;9007;3007</t>
+          <t>2008;4008;9008;3008</t>
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>28007</v>
+        <v>28008</v>
       </c>
       <c r="E158" s="3" t="n">
         <v>25</v>
@@ -3775,20 +3775,20 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>金雷斩邪剑</t>
+          <t>地脉重剑</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>2008;4008;9008;3008</t>
+          <t>2009;4009;9009;3009</t>
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>28008</v>
+        <v>28009</v>
       </c>
       <c r="E159" s="3" t="n">
         <v>25</v>
@@ -3796,20 +3796,20 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>地脉重剑</t>
+          <t>星陨长剑</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>2009;4009;9009;3009</t>
+          <t>2010;4010;27060;3010</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>28009</v>
+        <v>28010</v>
       </c>
       <c r="E160" s="3" t="n">
         <v>25</v>
@@ -3817,20 +3817,20 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>星陨长剑</t>
+          <t>虚空影剑</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>2010;4010;27060;3010</t>
+          <t>2011;4011;9011;3011</t>
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>28010</v>
+        <v>28011</v>
       </c>
       <c r="E161" s="3" t="n">
         <v>25</v>
@@ -3838,20 +3838,20 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>虚空影剑</t>
+          <t>九幽玄冥剑</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>2011;4011;9011;3011</t>
+          <t>2012;4012;9012;6012</t>
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>28011</v>
+        <v>28012</v>
       </c>
       <c r="E162" s="3" t="n">
         <v>25</v>
@@ -3859,20 +3859,20 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>九幽玄冥剑</t>
+          <t>太阳真光剑</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>2012;4012;9012;6012</t>
+          <t>2013;4013;9013;3013</t>
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>28012</v>
+        <v>28013</v>
       </c>
       <c r="E163" s="3" t="n">
         <v>25</v>
@@ -3880,20 +3880,20 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>太阳真光剑</t>
+          <t>太阴寒月剑</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>2013;4013;9013;3013</t>
+          <t>2014;4014;9014;3014</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>28013</v>
+        <v>28014</v>
       </c>
       <c r="E164" s="3" t="n">
         <v>25</v>
@@ -3901,20 +3901,20 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>太阴寒月剑</t>
+          <t>星河无极剑</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>2014;4014;9014;3014</t>
+          <t>2015;4015;9015;3015</t>
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>28014</v>
+        <v>28015</v>
       </c>
       <c r="E165" s="3" t="n">
         <v>25</v>
@@ -3922,20 +3922,20 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>星河无极剑</t>
+          <t>鸿蒙开天剑</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>2015;4015;9015;3015</t>
+          <t>2016;4016;9016;3016</t>
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>28015</v>
+        <v>28016</v>
       </c>
       <c r="E166" s="3" t="n">
         <v>25</v>
@@ -3943,62 +3943,62 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙开天剑</t>
+          <t>清风阵</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>2016;4016;9016;3016</t>
+          <t>13101;7001;9001</t>
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>28016</v>
+        <v>28017</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>清风阵</t>
+          <t>聚灵阵</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>13101;7001;9001</t>
+          <t>13102;7002;9002;4001</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>28017</v>
+        <v>28018</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>聚灵阵</t>
+          <t>铁壁阵</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>13102;7002;9002;4001</t>
+          <t>13103;7003;4002;9003</t>
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>28018</v>
+        <v>28019</v>
       </c>
       <c r="E169" s="3" t="n">
         <v>25</v>
@@ -4006,20 +4006,20 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>铁壁阵</t>
+          <t>三才锁灵阵</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>13103;7003;4002;9003</t>
+          <t>13104;7004;4004;9004</t>
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>28019</v>
+        <v>28020</v>
       </c>
       <c r="E170" s="3" t="n">
         <v>25</v>
@@ -4027,20 +4027,20 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>三才锁灵阵</t>
+          <t>四象寒冰阵</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>13104;7004;4004;9004</t>
+          <t>13105;7005;4005;3005</t>
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>28020</v>
+        <v>28021</v>
       </c>
       <c r="E171" s="3" t="n">
         <v>25</v>
@@ -4048,20 +4048,20 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>四象寒冰阵</t>
+          <t>烈焰困阵</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>13105;7005;4005;3005</t>
+          <t>13106;7006;4006;3006</t>
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>28021</v>
+        <v>28022</v>
       </c>
       <c r="E172" s="3" t="n">
         <v>25</v>
@@ -4069,20 +4069,20 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>烈焰困阵</t>
+          <t>厚土御阵</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>13106;7006;4006;3006</t>
+          <t>13107;7007;4007;3007</t>
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>28022</v>
+        <v>28023</v>
       </c>
       <c r="E173" s="3" t="n">
         <v>25</v>
@@ -4090,20 +4090,20 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>厚土御阵</t>
+          <t>五雷诛邪阵</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>13107;7007;4007;3007</t>
+          <t>13108;7008;4008;3008</t>
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>28023</v>
+        <v>28024</v>
       </c>
       <c r="E174" s="3" t="n">
         <v>25</v>
@@ -4111,20 +4111,20 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>五雷诛邪阵</t>
+          <t>地脉龙吟阵</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>13108;7008;4008;3008</t>
+          <t>13109;7009;4009;3009</t>
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>28024</v>
+        <v>28025</v>
       </c>
       <c r="E175" s="3" t="n">
         <v>25</v>
@@ -4132,20 +4132,20 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>地脉龙吟阵</t>
+          <t>星罗迷阵</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>13109;7009;4009;3009</t>
+          <t>13110;7010;4010;3010</t>
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>28025</v>
+        <v>28026</v>
       </c>
       <c r="E176" s="3" t="n">
         <v>25</v>
@@ -4153,20 +4153,20 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>星罗迷阵</t>
+          <t>九幻迷心阵</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>13110;7010;4010;3010</t>
+          <t>13111;7011;4011;3011</t>
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>28026</v>
+        <v>28027</v>
       </c>
       <c r="E177" s="3" t="n">
         <v>25</v>
@@ -4174,20 +4174,20 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>九幻迷心阵</t>
+          <t>九命续生阵</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>13111;7011;4011;3011</t>
+          <t>13112;7012;4012;9012</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>28027</v>
+        <v>28028</v>
       </c>
       <c r="E178" s="3" t="n">
         <v>25</v>
@@ -4195,20 +4195,20 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>九命续生阵</t>
+          <t>瑞兽祥云阵</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>13112;7012;4012;9012</t>
+          <t>13113;7013;4013;3013</t>
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>28028</v>
+        <v>28029</v>
       </c>
       <c r="E179" s="3" t="n">
         <v>25</v>
@@ -4216,20 +4216,20 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>瑞兽祥云阵</t>
+          <t>真龙御天阵</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>13113;7013;4013;3013</t>
+          <t>13114;7014;4014;3014</t>
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>28029</v>
+        <v>28030</v>
       </c>
       <c r="E180" s="3" t="n">
         <v>25</v>
@@ -4237,20 +4237,20 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>真龙御天阵</t>
+          <t>凤舞涅槃阵</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>13114;7014;4014;3014</t>
+          <t>13115;7015;4015;3015</t>
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>28030</v>
+        <v>28031</v>
       </c>
       <c r="E181" s="3" t="n">
         <v>25</v>
@@ -4258,20 +4258,20 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>凤舞涅槃阵</t>
+          <t>混沌归一阵</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>13115;7015;4015;3015</t>
+          <t>13116;7016;4016;3016</t>
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>28031</v>
+        <v>28032</v>
       </c>
       <c r="E182" s="3" t="n">
         <v>25</v>
@@ -4279,41 +4279,41 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>混沌归一阵</t>
+          <t>驱兽符</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>13116;7016;4016;3016</t>
+          <t>7001;8001;9001</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>28032</v>
+        <v>28033</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>驱兽符</t>
+          <t>避尘符</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>7001;8001;9001</t>
+          <t>7002;8002;9001</t>
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>28033</v>
+        <v>28034</v>
       </c>
       <c r="E184" s="3" t="n">
         <v>20</v>
@@ -4321,41 +4321,41 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>避尘符</t>
+          <t>火弹符</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>7002;8002;9001</t>
+          <t>7003;8003;9002;3002</t>
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>28034</v>
+        <v>28035</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>火弹符</t>
+          <t>金甲符</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>7003;8003;9002;3002</t>
+          <t>7004;8004;9002;3004</t>
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>28035</v>
+        <v>28036</v>
       </c>
       <c r="E186" s="3" t="n">
         <v>25</v>
@@ -4363,20 +4363,20 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>金甲符</t>
+          <t>冰锥符</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>7004;8004;9002;3004</t>
+          <t>7005;8005;9003;3005</t>
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>28036</v>
+        <v>28037</v>
       </c>
       <c r="E187" s="3" t="n">
         <v>25</v>
@@ -4384,20 +4384,20 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>冰锥符</t>
+          <t>炎爆符</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>7005;8005;9003;3005</t>
+          <t>7006;8006;9003;3006</t>
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>28037</v>
+        <v>28038</v>
       </c>
       <c r="E188" s="3" t="n">
         <v>25</v>
@@ -4405,20 +4405,20 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>炎爆符</t>
+          <t>青藤符</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>7006;8006;9003;3006</t>
+          <t>7007;8007;9004;3007</t>
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>28038</v>
+        <v>28039</v>
       </c>
       <c r="E189" s="3" t="n">
         <v>25</v>
@@ -4426,20 +4426,20 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>青藤符</t>
+          <t>五雷符</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>7007;8007;9004;3007</t>
+          <t>7008;8008;9004;3008</t>
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>28039</v>
+        <v>28040</v>
       </c>
       <c r="E190" s="3" t="n">
         <v>25</v>
@@ -4447,20 +4447,20 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>五雷符</t>
+          <t>地裂符</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>7008;8008;9004;3008</t>
+          <t>7009;8009;9005;3009</t>
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>28040</v>
+        <v>28041</v>
       </c>
       <c r="E191" s="3" t="n">
         <v>25</v>
@@ -4468,20 +4468,20 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>地裂符</t>
+          <t>星遁符</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>7009;8009;9005;3009</t>
+          <t>7010;8010;9005;3010</t>
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>28041</v>
+        <v>28042</v>
       </c>
       <c r="E192" s="3" t="n">
         <v>25</v>
@@ -4489,20 +4489,20 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>星遁符</t>
+          <t>幻身符</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>7010;8010;9005;3010</t>
+          <t>7011;8011;9006;3011</t>
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>28042</v>
+        <v>28043</v>
       </c>
       <c r="E193" s="3" t="n">
         <v>25</v>
@@ -4510,20 +4510,20 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>幻身符</t>
+          <t>续命符</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>7011;8011;9006;3011</t>
+          <t>7012;8012;9006;9012</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>28043</v>
+        <v>28044</v>
       </c>
       <c r="E194" s="3" t="n">
         <v>25</v>
@@ -4531,20 +4531,20 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>续命符</t>
+          <t>祥瑞符</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>7012;8012;9006;9012</t>
+          <t>7013;8013;9007;3013</t>
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>28044</v>
+        <v>28045</v>
       </c>
       <c r="E195" s="3" t="n">
         <v>25</v>
@@ -4552,20 +4552,20 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>祥瑞符</t>
+          <t>龙威符</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>7013;8013;9007;3013</t>
+          <t>7014;8014;9007;3014</t>
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>28045</v>
+        <v>28046</v>
       </c>
       <c r="E196" s="3" t="n">
         <v>25</v>
@@ -4573,20 +4573,20 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>龙威符</t>
+          <t>涅槃符</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>7014;8014;9007;3014</t>
+          <t>7015;8015;9008;3015</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>28046</v>
+        <v>28047</v>
       </c>
       <c r="E197" s="3" t="n">
         <v>25</v>
@@ -4594,20 +4594,20 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>涅槃符</t>
+          <t>混沌符</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>7015;8015;9008;3015</t>
+          <t>7016;8016;9008;3016</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>28047</v>
+        <v>28048</v>
       </c>
       <c r="E198" s="3" t="n">
         <v>25</v>
@@ -4615,62 +4615,62 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>混沌符</t>
+          <t>引气筑基散</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>7016;8016;9008;3016</t>
+          <t>1002;5002;9002</t>
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>28048</v>
+        <v>28049</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>引气筑基散</t>
+          <t>凝元破境丹</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>1002;5002;9002</t>
+          <t>1003;5004;9004;3004</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>28049</v>
+        <v>28050</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>凝元破境丹</t>
+          <t>筑基破障丹</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>1003;5004;9004;3004</t>
+          <t>1004;1005;27004;4004</t>
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>28050</v>
+        <v>28051</v>
       </c>
       <c r="E201" s="3" t="n">
         <v>25</v>
@@ -4678,20 +4678,20 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>筑基破障丹</t>
+          <t>固基培元丹</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>1004;1005;27004;4004</t>
+          <t>1005;1006;9006;4006</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>28051</v>
+        <v>28052</v>
       </c>
       <c r="E202" s="3" t="n">
         <v>25</v>
@@ -4699,20 +4699,20 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>固基培元丹</t>
+          <t>通玄化灵丹</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>1005;1006;9006;4006</t>
+          <t>1007;1008;9008;4008</t>
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>28052</v>
+        <v>28053</v>
       </c>
       <c r="E203" s="3" t="n">
         <v>25</v>
@@ -4720,20 +4720,20 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>通玄化灵丹</t>
+          <t>金丹破障丹</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>1007;1008;9008;4008</t>
+          <t>1009;1010;27007;4009</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>28053</v>
+        <v>28054</v>
       </c>
       <c r="E204" s="3" t="n">
         <v>25</v>
@@ -4741,20 +4741,20 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>金丹破障丹</t>
+          <t>凝丹化形丹</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>1009;1010;27007;4009</t>
+          <t>1009;1011;9011;4011</t>
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>28054</v>
+        <v>28055</v>
       </c>
       <c r="E205" s="3" t="n">
         <v>25</v>
@@ -4762,20 +4762,20 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>凝丹化形丹</t>
+          <t>九转金丹</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>1009;1011;9011;4011</t>
+          <t>1012;1011;9012;4012</t>
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>28055</v>
+        <v>28056</v>
       </c>
       <c r="E206" s="3" t="n">
         <v>25</v>
@@ -4783,20 +4783,20 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>九转金丹</t>
+          <t>元婴破障丹</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>1012;1011;9012;4012</t>
+          <t>1012;2009;27009;8012</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>28056</v>
+        <v>28057</v>
       </c>
       <c r="E207" s="3" t="n">
         <v>25</v>
@@ -4804,20 +4804,20 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>元婴破障丹</t>
+          <t>元婴凝神丹</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>1012;2009;27009;8012</t>
+          <t>7013;7014;9013;4013</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>28057</v>
+        <v>28058</v>
       </c>
       <c r="E208" s="3" t="n">
         <v>25</v>
@@ -4825,20 +4825,20 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>元婴凝神丹</t>
+          <t>元婴归元丹</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>7013;7014;9013;4013</t>
+          <t>7015;7014;9015;4014</t>
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>28058</v>
+        <v>28059</v>
       </c>
       <c r="E209" s="3" t="n">
         <v>25</v>
@@ -4846,43 +4846,22 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>元婴归元丹</t>
+          <t>化神渡劫丹</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>7015;7014;9015;4014</t>
+          <t>7016;8016;3016;4016</t>
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>28059</v>
+        <v>28060</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>化神渡劫丹</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="inlineStr">
-        <is>
-          <t>7016;8016;3016;4016</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="n">
-        <v>28060</v>
-      </c>
-      <c r="E211" s="3" t="n">
         <v>25</v>
       </c>
     </row>

--- a/config/xlsx/recipes.xlsx
+++ b/config/xlsx/recipes.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipes" sheetId="1" r:id="R55a2cb734af34506"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipes" sheetId="1" r:id="R6035760237fc4dc4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -419,7 +419,7 @@
         <x:v>27001</x:v>
       </x:c>
       <x:c r="E2" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -440,7 +440,7 @@
         <x:v>27002</x:v>
       </x:c>
       <x:c r="E3" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -461,7 +461,7 @@
         <x:v>27003</x:v>
       </x:c>
       <x:c r="E4" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -482,7 +482,7 @@
         <x:v>27004</x:v>
       </x:c>
       <x:c r="E5" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -503,7 +503,7 @@
         <x:v>27005</x:v>
       </x:c>
       <x:c r="E6" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -524,7 +524,7 @@
         <x:v>27006</x:v>
       </x:c>
       <x:c r="E7" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -545,7 +545,7 @@
         <x:v>27007</x:v>
       </x:c>
       <x:c r="E8" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -566,7 +566,7 @@
         <x:v>27008</x:v>
       </x:c>
       <x:c r="E9" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -587,7 +587,7 @@
         <x:v>27009</x:v>
       </x:c>
       <x:c r="E10" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -608,7 +608,7 @@
         <x:v>27010</x:v>
       </x:c>
       <x:c r="E11" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -629,7 +629,7 @@
         <x:v>27011</x:v>
       </x:c>
       <x:c r="E12" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -650,7 +650,7 @@
         <x:v>27012</x:v>
       </x:c>
       <x:c r="E13" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -671,7 +671,7 @@
         <x:v>27013</x:v>
       </x:c>
       <x:c r="E14" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -692,7 +692,7 @@
         <x:v>27014</x:v>
       </x:c>
       <x:c r="E15" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -713,7 +713,7 @@
         <x:v>27015</x:v>
       </x:c>
       <x:c r="E16" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -734,7 +734,7 @@
         <x:v>27016</x:v>
       </x:c>
       <x:c r="E17" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -755,7 +755,7 @@
         <x:v>27017</x:v>
       </x:c>
       <x:c r="E18" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -776,7 +776,7 @@
         <x:v>27018</x:v>
       </x:c>
       <x:c r="E19" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -797,7 +797,7 @@
         <x:v>27019</x:v>
       </x:c>
       <x:c r="E20" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -818,7 +818,7 @@
         <x:v>27020</x:v>
       </x:c>
       <x:c r="E21" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -839,7 +839,7 @@
         <x:v>27021</x:v>
       </x:c>
       <x:c r="E22" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -860,7 +860,7 @@
         <x:v>27022</x:v>
       </x:c>
       <x:c r="E23" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -881,7 +881,7 @@
         <x:v>27023</x:v>
       </x:c>
       <x:c r="E24" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -902,7 +902,7 @@
         <x:v>27024</x:v>
       </x:c>
       <x:c r="E25" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -923,7 +923,7 @@
         <x:v>27025</x:v>
       </x:c>
       <x:c r="E26" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -944,7 +944,7 @@
         <x:v>27026</x:v>
       </x:c>
       <x:c r="E27" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -965,7 +965,7 @@
         <x:v>27027</x:v>
       </x:c>
       <x:c r="E28" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -986,7 +986,7 @@
         <x:v>27028</x:v>
       </x:c>
       <x:c r="E29" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1007,7 +1007,7 @@
         <x:v>27029</x:v>
       </x:c>
       <x:c r="E30" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1028,7 +1028,7 @@
         <x:v>27030</x:v>
       </x:c>
       <x:c r="E31" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1049,7 +1049,7 @@
         <x:v>27031</x:v>
       </x:c>
       <x:c r="E32" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1070,7 +1070,7 @@
         <x:v>27081</x:v>
       </x:c>
       <x:c r="E33" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1091,7 +1091,7 @@
         <x:v>27033</x:v>
       </x:c>
       <x:c r="E34" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1112,7 +1112,7 @@
         <x:v>27034</x:v>
       </x:c>
       <x:c r="E35" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1133,7 +1133,7 @@
         <x:v>27035</x:v>
       </x:c>
       <x:c r="E36" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1154,7 +1154,7 @@
         <x:v>27036</x:v>
       </x:c>
       <x:c r="E37" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1175,7 +1175,7 @@
         <x:v>27037</x:v>
       </x:c>
       <x:c r="E38" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -1196,7 +1196,7 @@
         <x:v>27038</x:v>
       </x:c>
       <x:c r="E39" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1217,7 +1217,7 @@
         <x:v>27039</x:v>
       </x:c>
       <x:c r="E40" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -1238,7 +1238,7 @@
         <x:v>27040</x:v>
       </x:c>
       <x:c r="E41" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -1259,7 +1259,7 @@
         <x:v>27041</x:v>
       </x:c>
       <x:c r="E42" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -1280,7 +1280,7 @@
         <x:v>27042</x:v>
       </x:c>
       <x:c r="E43" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -1301,7 +1301,7 @@
         <x:v>27043</x:v>
       </x:c>
       <x:c r="E44" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -1322,7 +1322,7 @@
         <x:v>27044</x:v>
       </x:c>
       <x:c r="E45" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1343,7 +1343,7 @@
         <x:v>27045</x:v>
       </x:c>
       <x:c r="E46" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1364,7 +1364,7 @@
         <x:v>27046</x:v>
       </x:c>
       <x:c r="E47" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -1385,7 +1385,7 @@
         <x:v>27047</x:v>
       </x:c>
       <x:c r="E48" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1406,7 +1406,7 @@
         <x:v>27048</x:v>
       </x:c>
       <x:c r="E49" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1427,7 +1427,7 @@
         <x:v>27049</x:v>
       </x:c>
       <x:c r="E50" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -1448,7 +1448,7 @@
         <x:v>27050</x:v>
       </x:c>
       <x:c r="E51" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1469,7 +1469,7 @@
         <x:v>27051</x:v>
       </x:c>
       <x:c r="E52" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -1490,7 +1490,7 @@
         <x:v>27052</x:v>
       </x:c>
       <x:c r="E53" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -1511,7 +1511,7 @@
         <x:v>27053</x:v>
       </x:c>
       <x:c r="E54" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -1532,7 +1532,7 @@
         <x:v>27054</x:v>
       </x:c>
       <x:c r="E55" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -1553,7 +1553,7 @@
         <x:v>27055</x:v>
       </x:c>
       <x:c r="E56" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -1574,7 +1574,7 @@
         <x:v>27056</x:v>
       </x:c>
       <x:c r="E57" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -1595,7 +1595,7 @@
         <x:v>27057</x:v>
       </x:c>
       <x:c r="E58" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -1616,7 +1616,7 @@
         <x:v>27058</x:v>
       </x:c>
       <x:c r="E59" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -1637,7 +1637,7 @@
         <x:v>27059</x:v>
       </x:c>
       <x:c r="E60" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -1658,7 +1658,7 @@
         <x:v>27060</x:v>
       </x:c>
       <x:c r="E61" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -1679,7 +1679,7 @@
         <x:v>27061</x:v>
       </x:c>
       <x:c r="E62" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -1700,7 +1700,7 @@
         <x:v>27062</x:v>
       </x:c>
       <x:c r="E63" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -1721,7 +1721,7 @@
         <x:v>27063</x:v>
       </x:c>
       <x:c r="E64" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -1742,7 +1742,7 @@
         <x:v>27064</x:v>
       </x:c>
       <x:c r="E65" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -1763,7 +1763,7 @@
         <x:v>27065</x:v>
       </x:c>
       <x:c r="E66" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -1784,7 +1784,7 @@
         <x:v>27066</x:v>
       </x:c>
       <x:c r="E67" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -1805,7 +1805,7 @@
         <x:v>27067</x:v>
       </x:c>
       <x:c r="E68" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -1826,7 +1826,7 @@
         <x:v>27068</x:v>
       </x:c>
       <x:c r="E69" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -1847,7 +1847,7 @@
         <x:v>27069</x:v>
       </x:c>
       <x:c r="E70" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -1868,7 +1868,7 @@
         <x:v>27070</x:v>
       </x:c>
       <x:c r="E71" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -1889,7 +1889,7 @@
         <x:v>27071</x:v>
       </x:c>
       <x:c r="E72" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -1910,7 +1910,7 @@
         <x:v>27072</x:v>
       </x:c>
       <x:c r="E73" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -1931,7 +1931,7 @@
         <x:v>27073</x:v>
       </x:c>
       <x:c r="E74" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -1952,7 +1952,7 @@
         <x:v>27074</x:v>
       </x:c>
       <x:c r="E75" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -1973,7 +1973,7 @@
         <x:v>27075</x:v>
       </x:c>
       <x:c r="E76" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -1994,7 +1994,7 @@
         <x:v>27080</x:v>
       </x:c>
       <x:c r="E77" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -2015,7 +2015,7 @@
         <x:v>27077</x:v>
       </x:c>
       <x:c r="E78" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -2036,7 +2036,7 @@
         <x:v>27078</x:v>
       </x:c>
       <x:c r="E79" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -2057,7 +2057,7 @@
         <x:v>27079</x:v>
       </x:c>
       <x:c r="E80" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -2078,7 +2078,7 @@
         <x:v>27080</x:v>
       </x:c>
       <x:c r="E81" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -2099,7 +2099,7 @@
         <x:v>27081</x:v>
       </x:c>
       <x:c r="E82" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -2120,7 +2120,7 @@
         <x:v>27082</x:v>
       </x:c>
       <x:c r="E83" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -2141,7 +2141,7 @@
         <x:v>27083</x:v>
       </x:c>
       <x:c r="E84" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -2162,7 +2162,7 @@
         <x:v>27084</x:v>
       </x:c>
       <x:c r="E85" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -2183,7 +2183,7 @@
         <x:v>27085</x:v>
       </x:c>
       <x:c r="E86" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -2204,7 +2204,7 @@
         <x:v>27086</x:v>
       </x:c>
       <x:c r="E87" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -2225,7 +2225,7 @@
         <x:v>27087</x:v>
       </x:c>
       <x:c r="E88" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -2246,7 +2246,7 @@
         <x:v>27088</x:v>
       </x:c>
       <x:c r="E89" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -2267,7 +2267,7 @@
         <x:v>27089</x:v>
       </x:c>
       <x:c r="E90" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -2288,7 +2288,7 @@
         <x:v>27090</x:v>
       </x:c>
       <x:c r="E91" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -2309,7 +2309,7 @@
         <x:v>27091</x:v>
       </x:c>
       <x:c r="E92" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -2330,7 +2330,7 @@
         <x:v>27092</x:v>
       </x:c>
       <x:c r="E93" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -2351,7 +2351,7 @@
         <x:v>27093</x:v>
       </x:c>
       <x:c r="E94" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -2372,7 +2372,7 @@
         <x:v>27094</x:v>
       </x:c>
       <x:c r="E95" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -2393,7 +2393,7 @@
         <x:v>27095</x:v>
       </x:c>
       <x:c r="E96" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -2414,7 +2414,7 @@
         <x:v>27096</x:v>
       </x:c>
       <x:c r="E97" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -2435,7 +2435,7 @@
         <x:v>27097</x:v>
       </x:c>
       <x:c r="E98" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -2456,7 +2456,7 @@
         <x:v>27099</x:v>
       </x:c>
       <x:c r="E99" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -2477,7 +2477,7 @@
         <x:v>27100</x:v>
       </x:c>
       <x:c r="E100" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -2498,7 +2498,7 @@
         <x:v>27101</x:v>
       </x:c>
       <x:c r="E101" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -2519,7 +2519,7 @@
         <x:v>27102</x:v>
       </x:c>
       <x:c r="E102" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -2540,7 +2540,7 @@
         <x:v>27103</x:v>
       </x:c>
       <x:c r="E103" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -2561,7 +2561,7 @@
         <x:v>27104</x:v>
       </x:c>
       <x:c r="E104" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -2582,7 +2582,7 @@
         <x:v>27105</x:v>
       </x:c>
       <x:c r="E105" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -2603,7 +2603,7 @@
         <x:v>27106</x:v>
       </x:c>
       <x:c r="E106" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -2624,7 +2624,7 @@
         <x:v>27107</x:v>
       </x:c>
       <x:c r="E107" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -2645,7 +2645,7 @@
         <x:v>27108</x:v>
       </x:c>
       <x:c r="E108" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -2666,7 +2666,7 @@
         <x:v>27109</x:v>
       </x:c>
       <x:c r="E109" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -2687,7 +2687,7 @@
         <x:v>27110</x:v>
       </x:c>
       <x:c r="E110" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -2708,7 +2708,7 @@
         <x:v>27111</x:v>
       </x:c>
       <x:c r="E111" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -2729,7 +2729,7 @@
         <x:v>27112</x:v>
       </x:c>
       <x:c r="E112" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -2750,7 +2750,7 @@
         <x:v>27113</x:v>
       </x:c>
       <x:c r="E113" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -2771,7 +2771,7 @@
         <x:v>27114</x:v>
       </x:c>
       <x:c r="E114" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -2792,7 +2792,7 @@
         <x:v>27115</x:v>
       </x:c>
       <x:c r="E115" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -2813,7 +2813,7 @@
         <x:v>27116</x:v>
       </x:c>
       <x:c r="E116" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -2834,7 +2834,7 @@
         <x:v>27117</x:v>
       </x:c>
       <x:c r="E117" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -2855,7 +2855,7 @@
         <x:v>27118</x:v>
       </x:c>
       <x:c r="E118" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -2876,7 +2876,7 @@
         <x:v>27119</x:v>
       </x:c>
       <x:c r="E119" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -2897,7 +2897,7 @@
         <x:v>27120</x:v>
       </x:c>
       <x:c r="E120" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -2918,7 +2918,7 @@
         <x:v>27121</x:v>
       </x:c>
       <x:c r="E121" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -2939,7 +2939,7 @@
         <x:v>27122</x:v>
       </x:c>
       <x:c r="E122" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -2960,7 +2960,7 @@
         <x:v>27123</x:v>
       </x:c>
       <x:c r="E123" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -2981,7 +2981,7 @@
         <x:v>27124</x:v>
       </x:c>
       <x:c r="E124" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -3002,7 +3002,7 @@
         <x:v>27125</x:v>
       </x:c>
       <x:c r="E125" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -3023,7 +3023,7 @@
         <x:v>27126</x:v>
       </x:c>
       <x:c r="E126" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -3044,7 +3044,7 @@
         <x:v>27127</x:v>
       </x:c>
       <x:c r="E127" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -3065,7 +3065,7 @@
         <x:v>27128</x:v>
       </x:c>
       <x:c r="E128" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -3086,7 +3086,7 @@
         <x:v>27129</x:v>
       </x:c>
       <x:c r="E129" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -3107,7 +3107,7 @@
         <x:v>27130</x:v>
       </x:c>
       <x:c r="E130" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -3128,7 +3128,7 @@
         <x:v>27131</x:v>
       </x:c>
       <x:c r="E131" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -3149,7 +3149,7 @@
         <x:v>27132</x:v>
       </x:c>
       <x:c r="E132" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -3170,7 +3170,7 @@
         <x:v>27133</x:v>
       </x:c>
       <x:c r="E133" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -3191,7 +3191,7 @@
         <x:v>27134</x:v>
       </x:c>
       <x:c r="E134" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -3212,7 +3212,7 @@
         <x:v>27135</x:v>
       </x:c>
       <x:c r="E135" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -3233,7 +3233,7 @@
         <x:v>27136</x:v>
       </x:c>
       <x:c r="E136" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -3254,7 +3254,7 @@
         <x:v>27137</x:v>
       </x:c>
       <x:c r="E137" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -3275,7 +3275,7 @@
         <x:v>27138</x:v>
       </x:c>
       <x:c r="E138" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3296,7 +3296,7 @@
         <x:v>27139</x:v>
       </x:c>
       <x:c r="E139" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -3317,7 +3317,7 @@
         <x:v>27140</x:v>
       </x:c>
       <x:c r="E140" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -3338,7 +3338,7 @@
         <x:v>27141</x:v>
       </x:c>
       <x:c r="E141" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -3359,7 +3359,7 @@
         <x:v>27142</x:v>
       </x:c>
       <x:c r="E142" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -3380,7 +3380,7 @@
         <x:v>27143</x:v>
       </x:c>
       <x:c r="E143" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -3401,7 +3401,7 @@
         <x:v>27144</x:v>
       </x:c>
       <x:c r="E144" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -3422,7 +3422,7 @@
         <x:v>27145</x:v>
       </x:c>
       <x:c r="E145" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -3443,7 +3443,7 @@
         <x:v>27146</x:v>
       </x:c>
       <x:c r="E146" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -3464,7 +3464,7 @@
         <x:v>27147</x:v>
       </x:c>
       <x:c r="E147" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -3485,7 +3485,7 @@
         <x:v>27148</x:v>
       </x:c>
       <x:c r="E148" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -3506,7 +3506,7 @@
         <x:v>27149</x:v>
       </x:c>
       <x:c r="E149" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -3527,7 +3527,7 @@
         <x:v>27150</x:v>
       </x:c>
       <x:c r="E150" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -3548,7 +3548,7 @@
         <x:v>28001</x:v>
       </x:c>
       <x:c r="E151" s="3" t="n">
-        <x:v>15</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -3569,7 +3569,7 @@
         <x:v>28002</x:v>
       </x:c>
       <x:c r="E152" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -3590,7 +3590,7 @@
         <x:v>28003</x:v>
       </x:c>
       <x:c r="E153" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -3611,7 +3611,7 @@
         <x:v>28004</x:v>
       </x:c>
       <x:c r="E154" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -3632,7 +3632,7 @@
         <x:v>28005</x:v>
       </x:c>
       <x:c r="E155" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -3653,7 +3653,7 @@
         <x:v>28006</x:v>
       </x:c>
       <x:c r="E156" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -3674,7 +3674,7 @@
         <x:v>28007</x:v>
       </x:c>
       <x:c r="E157" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -3695,7 +3695,7 @@
         <x:v>28008</x:v>
       </x:c>
       <x:c r="E158" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -3716,7 +3716,7 @@
         <x:v>28009</x:v>
       </x:c>
       <x:c r="E159" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -3737,7 +3737,7 @@
         <x:v>28010</x:v>
       </x:c>
       <x:c r="E160" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -3758,7 +3758,7 @@
         <x:v>28011</x:v>
       </x:c>
       <x:c r="E161" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -3779,7 +3779,7 @@
         <x:v>28012</x:v>
       </x:c>
       <x:c r="E162" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -3800,7 +3800,7 @@
         <x:v>28013</x:v>
       </x:c>
       <x:c r="E163" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -3821,7 +3821,7 @@
         <x:v>28014</x:v>
       </x:c>
       <x:c r="E164" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -3842,7 +3842,7 @@
         <x:v>28015</x:v>
       </x:c>
       <x:c r="E165" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -3863,7 +3863,7 @@
         <x:v>28016</x:v>
       </x:c>
       <x:c r="E166" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -3884,7 +3884,7 @@
         <x:v>28017</x:v>
       </x:c>
       <x:c r="E167" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -3905,7 +3905,7 @@
         <x:v>28018</x:v>
       </x:c>
       <x:c r="E168" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -3926,7 +3926,7 @@
         <x:v>28019</x:v>
       </x:c>
       <x:c r="E169" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -3947,7 +3947,7 @@
         <x:v>28020</x:v>
       </x:c>
       <x:c r="E170" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -3968,7 +3968,7 @@
         <x:v>28021</x:v>
       </x:c>
       <x:c r="E171" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -3989,7 +3989,7 @@
         <x:v>28022</x:v>
       </x:c>
       <x:c r="E172" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -4010,7 +4010,7 @@
         <x:v>28023</x:v>
       </x:c>
       <x:c r="E173" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -4031,7 +4031,7 @@
         <x:v>28024</x:v>
       </x:c>
       <x:c r="E174" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -4052,7 +4052,7 @@
         <x:v>28025</x:v>
       </x:c>
       <x:c r="E175" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -4073,7 +4073,7 @@
         <x:v>28026</x:v>
       </x:c>
       <x:c r="E176" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -4094,7 +4094,7 @@
         <x:v>28027</x:v>
       </x:c>
       <x:c r="E177" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -4115,7 +4115,7 @@
         <x:v>28028</x:v>
       </x:c>
       <x:c r="E178" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -4136,7 +4136,7 @@
         <x:v>28029</x:v>
       </x:c>
       <x:c r="E179" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -4157,7 +4157,7 @@
         <x:v>28030</x:v>
       </x:c>
       <x:c r="E180" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -4178,7 +4178,7 @@
         <x:v>28031</x:v>
       </x:c>
       <x:c r="E181" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -4199,7 +4199,7 @@
         <x:v>28032</x:v>
       </x:c>
       <x:c r="E182" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -4220,7 +4220,7 @@
         <x:v>28033</x:v>
       </x:c>
       <x:c r="E183" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -4241,7 +4241,7 @@
         <x:v>28034</x:v>
       </x:c>
       <x:c r="E184" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -4262,7 +4262,7 @@
         <x:v>28035</x:v>
       </x:c>
       <x:c r="E185" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -4283,7 +4283,7 @@
         <x:v>28036</x:v>
       </x:c>
       <x:c r="E186" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -4304,7 +4304,7 @@
         <x:v>28037</x:v>
       </x:c>
       <x:c r="E187" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -4325,7 +4325,7 @@
         <x:v>28038</x:v>
       </x:c>
       <x:c r="E188" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -4346,7 +4346,7 @@
         <x:v>28039</x:v>
       </x:c>
       <x:c r="E189" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -4367,7 +4367,7 @@
         <x:v>28040</x:v>
       </x:c>
       <x:c r="E190" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -4388,7 +4388,7 @@
         <x:v>28041</x:v>
       </x:c>
       <x:c r="E191" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -4409,7 +4409,7 @@
         <x:v>28042</x:v>
       </x:c>
       <x:c r="E192" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -4430,7 +4430,7 @@
         <x:v>28043</x:v>
       </x:c>
       <x:c r="E193" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -4451,7 +4451,7 @@
         <x:v>28044</x:v>
       </x:c>
       <x:c r="E194" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -4472,7 +4472,7 @@
         <x:v>28045</x:v>
       </x:c>
       <x:c r="E195" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>21600</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -4493,7 +4493,7 @@
         <x:v>28046</x:v>
       </x:c>
       <x:c r="E196" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -4514,7 +4514,7 @@
         <x:v>28047</x:v>
       </x:c>
       <x:c r="E197" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -4535,7 +4535,7 @@
         <x:v>28048</x:v>
       </x:c>
       <x:c r="E198" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -4556,7 +4556,7 @@
         <x:v>28049</x:v>
       </x:c>
       <x:c r="E199" s="3" t="n">
-        <x:v>20</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -4577,7 +4577,7 @@
         <x:v>28050</x:v>
       </x:c>
       <x:c r="E200" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -4598,7 +4598,7 @@
         <x:v>28051</x:v>
       </x:c>
       <x:c r="E201" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -4619,7 +4619,7 @@
         <x:v>28052</x:v>
       </x:c>
       <x:c r="E202" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -4640,7 +4640,7 @@
         <x:v>28053</x:v>
       </x:c>
       <x:c r="E203" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -4661,7 +4661,7 @@
         <x:v>28054</x:v>
       </x:c>
       <x:c r="E204" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -4682,7 +4682,7 @@
         <x:v>28055</x:v>
       </x:c>
       <x:c r="E205" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>10800</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -4703,7 +4703,7 @@
         <x:v>28056</x:v>
       </x:c>
       <x:c r="E206" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -4724,7 +4724,7 @@
         <x:v>28057</x:v>
       </x:c>
       <x:c r="E207" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -4745,7 +4745,7 @@
         <x:v>28058</x:v>
       </x:c>
       <x:c r="E208" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -4766,7 +4766,7 @@
         <x:v>28059</x:v>
       </x:c>
       <x:c r="E209" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>36000</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -4787,7 +4787,7 @@
         <x:v>28060</x:v>
       </x:c>
       <x:c r="E210" s="3" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -4804,7 +4804,7 @@
         <x:v>28101</x:v>
       </x:c>
       <x:c r="E211" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -4821,7 +4821,7 @@
         <x:v>28102</x:v>
       </x:c>
       <x:c r="E212" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -4838,7 +4838,7 @@
         <x:v>28103</x:v>
       </x:c>
       <x:c r="E213" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -4855,7 +4855,7 @@
         <x:v>28104</x:v>
       </x:c>
       <x:c r="E214" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -4872,7 +4872,7 @@
         <x:v>28105</x:v>
       </x:c>
       <x:c r="E215" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -4889,7 +4889,7 @@
         <x:v>28106</x:v>
       </x:c>
       <x:c r="E216" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -4906,7 +4906,7 @@
         <x:v>28107</x:v>
       </x:c>
       <x:c r="E217" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -4923,7 +4923,7 @@
         <x:v>28108</x:v>
       </x:c>
       <x:c r="E218" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -4940,7 +4940,7 @@
         <x:v>28109</x:v>
       </x:c>
       <x:c r="E219" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -4957,7 +4957,7 @@
         <x:v>28110</x:v>
       </x:c>
       <x:c r="E220" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -4974,7 +4974,7 @@
         <x:v>28111</x:v>
       </x:c>
       <x:c r="E221" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -4991,7 +4991,7 @@
         <x:v>28112</x:v>
       </x:c>
       <x:c r="E222" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -5008,7 +5008,7 @@
         <x:v>28113</x:v>
       </x:c>
       <x:c r="E223" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -5025,7 +5025,7 @@
         <x:v>28114</x:v>
       </x:c>
       <x:c r="E224" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -5042,7 +5042,7 @@
         <x:v>28115</x:v>
       </x:c>
       <x:c r="E225" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -5059,7 +5059,7 @@
         <x:v>28116</x:v>
       </x:c>
       <x:c r="E226" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
@@ -5076,7 +5076,7 @@
         <x:v>28117</x:v>
       </x:c>
       <x:c r="E227" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -5093,7 +5093,7 @@
         <x:v>28118</x:v>
       </x:c>
       <x:c r="E228" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
@@ -5110,7 +5110,7 @@
         <x:v>28119</x:v>
       </x:c>
       <x:c r="E229" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -5127,7 +5127,7 @@
         <x:v>28120</x:v>
       </x:c>
       <x:c r="E230" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -5144,7 +5144,7 @@
         <x:v>28121</x:v>
       </x:c>
       <x:c r="E231" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -5161,7 +5161,7 @@
         <x:v>28122</x:v>
       </x:c>
       <x:c r="E232" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
@@ -5178,7 +5178,7 @@
         <x:v>28123</x:v>
       </x:c>
       <x:c r="E233" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
@@ -5195,7 +5195,7 @@
         <x:v>28124</x:v>
       </x:c>
       <x:c r="E234" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -5212,7 +5212,7 @@
         <x:v>28125</x:v>
       </x:c>
       <x:c r="E235" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -5229,7 +5229,7 @@
         <x:v>28126</x:v>
       </x:c>
       <x:c r="E236" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -5246,7 +5246,7 @@
         <x:v>28127</x:v>
       </x:c>
       <x:c r="E237" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -5263,7 +5263,7 @@
         <x:v>28128</x:v>
       </x:c>
       <x:c r="E238" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
@@ -5280,7 +5280,7 @@
         <x:v>28129</x:v>
       </x:c>
       <x:c r="E239" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -5297,7 +5297,7 @@
         <x:v>28130</x:v>
       </x:c>
       <x:c r="E240" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -5314,7 +5314,7 @@
         <x:v>28131</x:v>
       </x:c>
       <x:c r="E241" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
@@ -5331,7 +5331,7 @@
         <x:v>28132</x:v>
       </x:c>
       <x:c r="E242" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -5348,7 +5348,7 @@
         <x:v>28133</x:v>
       </x:c>
       <x:c r="E243" s="4" t="n">
-        <x:v>25</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -5365,7 +5365,7 @@
         <x:v>28134</x:v>
       </x:c>
       <x:c r="E244" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -5382,7 +5382,7 @@
         <x:v>28135</x:v>
       </x:c>
       <x:c r="E245" s="4" t="n">
-        <x:v>25</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -5399,7 +5399,7 @@
         <x:v>28136</x:v>
       </x:c>
       <x:c r="E246" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="247">
@@ -5416,7 +5416,7 @@
         <x:v>28137</x:v>
       </x:c>
       <x:c r="E247" s="4" t="n">
-        <x:v>25</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="248">
@@ -5433,7 +5433,7 @@
         <x:v>28138</x:v>
       </x:c>
       <x:c r="E248" s="4" t="n">
-        <x:v>25</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
@@ -5450,7 +5450,7 @@
         <x:v>28139</x:v>
       </x:c>
       <x:c r="E249" s="4" t="n">
-        <x:v>25</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -5467,7 +5467,7 @@
         <x:v>28140</x:v>
       </x:c>
       <x:c r="E250" s="4" t="n">
-        <x:v>25</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
@@ -5484,7 +5484,7 @@
         <x:v>28141</x:v>
       </x:c>
       <x:c r="E251" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -5501,7 +5501,7 @@
         <x:v>28142</x:v>
       </x:c>
       <x:c r="E252" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="253">
@@ -5518,7 +5518,7 @@
         <x:v>28143</x:v>
       </x:c>
       <x:c r="E253" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="254">
@@ -5535,7 +5535,7 @@
         <x:v>28144</x:v>
       </x:c>
       <x:c r="E254" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>1200</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
@@ -5552,7 +5552,7 @@
         <x:v>28145</x:v>
       </x:c>
       <x:c r="E255" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -5569,7 +5569,7 @@
         <x:v>28146</x:v>
       </x:c>
       <x:c r="E256" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>3600</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
@@ -5586,7 +5586,7 @@
         <x:v>28147</x:v>
       </x:c>
       <x:c r="E257" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -5603,7 +5603,7 @@
         <x:v>28148</x:v>
       </x:c>
       <x:c r="E258" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>14400</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -5620,7 +5620,7 @@
         <x:v>28149</x:v>
       </x:c>
       <x:c r="E259" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -5637,7 +5637,7 @@
         <x:v>28150</x:v>
       </x:c>
       <x:c r="E260" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>43200</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/xlsx/recipes.xlsx
+++ b/config/xlsx/recipes.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipes" sheetId="1" r:id="R6035760237fc4dc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipes" sheetId="1" r:id="R5457bb324ef147f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -375,45 +375,31 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ingredients</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">result</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">craft_time</x:t>
-        </x:is>
+      <x:c r="A1" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="str">
+        <x:v>ingredients</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="str">
+        <x:v>result</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="str">
+        <x:v>craft_time</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">养气散</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5001;9001</x:t>
-        </x:is>
+      <x:c r="B2" s="2" t="str">
+        <x:v>养气散</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="str">
+        <x:v>5001;9001</x:v>
       </x:c>
       <x:c r="D2" s="3" t="n">
         <x:v>27001</x:v>
@@ -426,15 +412,11 @@
       <x:c r="A3" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">引气丸</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5002;9002</x:t>
-        </x:is>
+      <x:c r="B3" s="2" t="str">
+        <x:v>引气丸</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="str">
+        <x:v>5002;9002</x:v>
       </x:c>
       <x:c r="D3" s="3" t="n">
         <x:v>27002</x:v>
@@ -447,15 +429,11 @@
       <x:c r="A4" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">固元粉</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5003;1001</x:t>
-        </x:is>
+      <x:c r="B4" s="2" t="str">
+        <x:v>固元粉</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="str">
+        <x:v>5003;1001</x:v>
       </x:c>
       <x:c r="D4" s="3" t="n">
         <x:v>27003</x:v>
@@ -468,15 +446,11 @@
       <x:c r="A5" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">培元丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5004;1002;9003</x:t>
-        </x:is>
+      <x:c r="B5" s="2" t="str">
+        <x:v>培元丹</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="str">
+        <x:v>5004;1002;9003</x:v>
       </x:c>
       <x:c r="D5" s="3" t="n">
         <x:v>27004</x:v>
@@ -489,15 +463,11 @@
       <x:c r="A6" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">灵髓丸</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5005;1003;9004</x:t>
-        </x:is>
+      <x:c r="B6" s="2" t="str">
+        <x:v>灵髓丸</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="str">
+        <x:v>5005;1003;9004</x:v>
       </x:c>
       <x:c r="D6" s="3" t="n">
         <x:v>27005</x:v>
@@ -510,15 +480,11 @@
       <x:c r="A7" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">黄芽丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1004;6004</x:t>
-        </x:is>
+      <x:c r="B7" s="2" t="str">
+        <x:v>黄芽丹</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>1004;6004</x:v>
       </x:c>
       <x:c r="D7" s="3" t="n">
         <x:v>27006</x:v>
@@ -531,15 +497,11 @@
       <x:c r="A8" s="2" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">小还丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1005;6005;9005;3001</x:t>
-        </x:is>
+      <x:c r="B8" s="2" t="str">
+        <x:v>小还丹</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>1005;6005;9005;3001</x:v>
       </x:c>
       <x:c r="D8" s="3" t="n">
         <x:v>27007</x:v>
@@ -552,15 +514,11 @@
       <x:c r="A9" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">赤阳丸</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1006;6006;12006;3002</x:t>
-        </x:is>
+      <x:c r="B9" s="2" t="str">
+        <x:v>赤阳丸</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>1006;6006;9006;3002</x:v>
       </x:c>
       <x:c r="D9" s="3" t="n">
         <x:v>27008</x:v>
@@ -573,15 +531,11 @@
       <x:c r="A10" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青冥丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1007;6007;9007;3003</x:t>
-        </x:is>
+      <x:c r="B10" s="2" t="str">
+        <x:v>青冥丹</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>1007;6007;9007;3003</x:v>
       </x:c>
       <x:c r="D10" s="3" t="n">
         <x:v>27009</x:v>
@@ -594,15 +548,11 @@
       <x:c r="A11" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄金散</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1008;6008;9008</x:t>
-        </x:is>
+      <x:c r="B11" s="2" t="str">
+        <x:v>玄金散</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>1008;6008;9008</x:v>
       </x:c>
       <x:c r="D11" s="3" t="n">
         <x:v>27010</x:v>
@@ -615,15 +565,11 @@
       <x:c r="A12" s="2" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">冰魄丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1009;7005;8005;3005</x:t>
-        </x:is>
+      <x:c r="B12" s="2" t="str">
+        <x:v>冰魄丹</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>1009;7005;8005;3005</x:v>
       </x:c>
       <x:c r="D12" s="3" t="n">
         <x:v>27011</x:v>
@@ -636,15 +582,11 @@
       <x:c r="A13" s="2" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">火灵丸</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1010;7006;8006;3006</x:t>
-        </x:is>
+      <x:c r="B13" s="2" t="str">
+        <x:v>火灵丸</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>1010;7006;8006;3006</x:v>
       </x:c>
       <x:c r="D13" s="3" t="n">
         <x:v>27012</x:v>
@@ -657,15 +599,11 @@
       <x:c r="A14" s="2" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青玄丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1011;7007;8007;3007</x:t>
-        </x:is>
+      <x:c r="B14" s="2" t="str">
+        <x:v>青玄丹</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>1011;7007;8007;3007</x:v>
       </x:c>
       <x:c r="D14" s="3" t="n">
         <x:v>27013</x:v>
@@ -678,15 +616,11 @@
       <x:c r="A15" s="2" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">五雷丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1012;7008;8008;3008</x:t>
-        </x:is>
+      <x:c r="B15" s="2" t="str">
+        <x:v>五雷丹</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>1012;7008;8008;3008</x:v>
       </x:c>
       <x:c r="D15" s="3" t="n">
         <x:v>27014</x:v>
@@ -699,15 +633,11 @@
       <x:c r="A16" s="2" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地龙丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7009;8009;3009;6009</x:t>
-        </x:is>
+      <x:c r="B16" s="2" t="str">
+        <x:v>地龙丹</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="str">
+        <x:v>7009;8009;3009;6009</x:v>
       </x:c>
       <x:c r="D16" s="3" t="n">
         <x:v>27015</x:v>
@@ -720,15 +650,11 @@
       <x:c r="A17" s="2" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星狼丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7010;8010;3010;6010</x:t>
-        </x:is>
+      <x:c r="B17" s="2" t="str">
+        <x:v>星狼丹</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="str">
+        <x:v>7010;8010;3010;6010</x:v>
       </x:c>
       <x:c r="D17" s="3" t="n">
         <x:v>27016</x:v>
@@ -741,15 +667,11 @@
       <x:c r="A18" s="2" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫狐丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7011;8011;3011;6011</x:t>
-        </x:is>
+      <x:c r="B18" s="2" t="str">
+        <x:v>紫狐丹</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="str">
+        <x:v>7011;8011;3011;6011</x:v>
       </x:c>
       <x:c r="D18" s="3" t="n">
         <x:v>27017</x:v>
@@ -762,15 +684,11 @@
       <x:c r="A19" s="2" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九命丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7012;8012;9012;6012</x:t>
-        </x:is>
+      <x:c r="B19" s="2" t="str">
+        <x:v>九命丹</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="str">
+        <x:v>7012;8012;9012;6012</x:v>
       </x:c>
       <x:c r="D19" s="3" t="n">
         <x:v>27018</x:v>
@@ -783,15 +701,11 @@
       <x:c r="A20" s="2" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B20" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地皇丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5009;5012;12009</x:t>
-        </x:is>
+      <x:c r="B20" s="2" t="str">
+        <x:v>地皇丹</x:v>
+      </x:c>
+      <x:c r="C20" s="3" t="str">
+        <x:v>5009;5012;9009</x:v>
       </x:c>
       <x:c r="D20" s="3" t="n">
         <x:v>27019</x:v>
@@ -804,15 +718,11 @@
       <x:c r="A21" s="2" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星芒丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5010;5011;9010</x:t>
-        </x:is>
+      <x:c r="B21" s="2" t="str">
+        <x:v>星芒丹</x:v>
+      </x:c>
+      <x:c r="C21" s="3" t="str">
+        <x:v>5010;5011;9010</x:v>
       </x:c>
       <x:c r="D21" s="3" t="n">
         <x:v>27020</x:v>
@@ -825,15 +735,11 @@
       <x:c r="A22" s="2" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B22" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫府金丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C22" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5011;9011;1010</x:t>
-        </x:is>
+      <x:c r="B22" s="2" t="str">
+        <x:v>紫府金丹</x:v>
+      </x:c>
+      <x:c r="C22" s="3" t="str">
+        <x:v>5011;9011;1010</x:v>
       </x:c>
       <x:c r="D22" s="3" t="n">
         <x:v>27021</x:v>
@@ -846,15 +752,11 @@
       <x:c r="A23" s="2" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B23" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍还魂丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C23" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5012;9012;1012</x:t>
-        </x:is>
+      <x:c r="B23" s="2" t="str">
+        <x:v>九窍还魂丹</x:v>
+      </x:c>
+      <x:c r="C23" s="3" t="str">
+        <x:v>5012;9012;1012</x:v>
       </x:c>
       <x:c r="D23" s="3" t="n">
         <x:v>27022</x:v>
@@ -867,15 +769,11 @@
       <x:c r="A24" s="2" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B24" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">麒麟丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C24" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7013;8013;12013</x:t>
-        </x:is>
+      <x:c r="B24" s="2" t="str">
+        <x:v>麒麟丹</x:v>
+      </x:c>
+      <x:c r="C24" s="3" t="str">
+        <x:v>7013;8013;9013</x:v>
       </x:c>
       <x:c r="D24" s="3" t="n">
         <x:v>27023</x:v>
@@ -888,15 +786,11 @@
       <x:c r="A25" s="2" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B25" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">真龙丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C25" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7014;8014;12014</x:t>
-        </x:is>
+      <x:c r="B25" s="2" t="str">
+        <x:v>真龙丹</x:v>
+      </x:c>
+      <x:c r="C25" s="3" t="str">
+        <x:v>7014;8014;9014</x:v>
       </x:c>
       <x:c r="D25" s="3" t="n">
         <x:v>27024</x:v>
@@ -909,15 +803,11 @@
       <x:c r="A26" s="2" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B26" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤凰丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C26" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7015;8015;9015</x:t>
-        </x:is>
+      <x:c r="B26" s="2" t="str">
+        <x:v>凤凰丹</x:v>
+      </x:c>
+      <x:c r="C26" s="3" t="str">
+        <x:v>7015;8015;9015</x:v>
       </x:c>
       <x:c r="D26" s="3" t="n">
         <x:v>27025</x:v>
@@ -930,15 +820,11 @@
       <x:c r="A27" s="2" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C27" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7016;8016;9016</x:t>
-        </x:is>
+      <x:c r="B27" s="2" t="str">
+        <x:v>混沌丹</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="str">
+        <x:v>7016;8016;9016</x:v>
       </x:c>
       <x:c r="D27" s="3" t="n">
         <x:v>27026</x:v>
@@ -951,15 +837,11 @@
       <x:c r="A28" s="2" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B28" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅槃丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C28" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5013;6013;3013</x:t>
-        </x:is>
+      <x:c r="B28" s="2" t="str">
+        <x:v>涅槃丹</x:v>
+      </x:c>
+      <x:c r="C28" s="3" t="str">
+        <x:v>5013;6013;3013</x:v>
       </x:c>
       <x:c r="D28" s="3" t="n">
         <x:v>27027</x:v>
@@ -972,15 +854,11 @@
       <x:c r="A29" s="2" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B29" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙牙丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C29" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5014;6014;3014</x:t>
-        </x:is>
+      <x:c r="B29" s="2" t="str">
+        <x:v>龙牙丹</x:v>
+      </x:c>
+      <x:c r="C29" s="3" t="str">
+        <x:v>5014;6014;3014</x:v>
       </x:c>
       <x:c r="D29" s="3" t="n">
         <x:v>27028</x:v>
@@ -993,15 +871,11 @@
       <x:c r="A30" s="2" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B30" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤羽金丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C30" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5015;6015;3015</x:t>
-        </x:is>
+      <x:c r="B30" s="2" t="str">
+        <x:v>凤羽金丹</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="str">
+        <x:v>5015;6015;3015</x:v>
       </x:c>
       <x:c r="D30" s="3" t="n">
         <x:v>27029</x:v>
@@ -1014,15 +888,11 @@
       <x:c r="A31" s="2" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B31" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌玄丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C31" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5016;6016;3016</x:t>
-        </x:is>
+      <x:c r="B31" s="2" t="str">
+        <x:v>混沌玄丹</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="str">
+        <x:v>5016;6016;3016</x:v>
       </x:c>
       <x:c r="D31" s="3" t="n">
         <x:v>27030</x:v>
@@ -1035,15 +905,11 @@
       <x:c r="A32" s="2" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B32" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">筑基丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C32" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27004;27004</x:t>
-        </x:is>
+      <x:c r="B32" s="2" t="str">
+        <x:v>筑基丹</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="str">
+        <x:v>27004;27004</x:v>
       </x:c>
       <x:c r="D32" s="3" t="n">
         <x:v>27031</x:v>
@@ -1056,15 +922,11 @@
       <x:c r="A33" s="2" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B33" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">聚灵大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C33" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27002;9004</x:t>
-        </x:is>
+      <x:c r="B33" s="2" t="str">
+        <x:v>聚灵大丹</x:v>
+      </x:c>
+      <x:c r="C33" s="3" t="str">
+        <x:v>27002;9004</x:v>
       </x:c>
       <x:c r="D33" s="3" t="n">
         <x:v>27081</x:v>
@@ -1077,15 +939,11 @@
       <x:c r="A34" s="2" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B34" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">培元大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C34" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27003;6004;5004</x:t>
-        </x:is>
+      <x:c r="B34" s="2" t="str">
+        <x:v>培元大丹</x:v>
+      </x:c>
+      <x:c r="C34" s="3" t="str">
+        <x:v>27003;6004;5004</x:v>
       </x:c>
       <x:c r="D34" s="3" t="n">
         <x:v>27033</x:v>
@@ -1098,15 +956,11 @@
       <x:c r="A35" s="2" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B35" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄冰大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C35" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27005;6005;3005</x:t>
-        </x:is>
+      <x:c r="B35" s="2" t="str">
+        <x:v>玄冰大丹</x:v>
+      </x:c>
+      <x:c r="C35" s="3" t="str">
+        <x:v>27005;6005;3005</x:v>
       </x:c>
       <x:c r="D35" s="3" t="n">
         <x:v>27034</x:v>
@@ -1119,15 +973,11 @@
       <x:c r="A36" s="2" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B36" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">赤阳大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C36" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27008;6006;3006</x:t>
-        </x:is>
+      <x:c r="B36" s="2" t="str">
+        <x:v>赤阳大丹</x:v>
+      </x:c>
+      <x:c r="C36" s="3" t="str">
+        <x:v>27008;6006;3006</x:v>
       </x:c>
       <x:c r="D36" s="3" t="n">
         <x:v>27035</x:v>
@@ -1140,15 +990,11 @@
       <x:c r="A37" s="2" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B37" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青木大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C37" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27009;6007;3007</x:t>
-        </x:is>
+      <x:c r="B37" s="2" t="str">
+        <x:v>青木大丹</x:v>
+      </x:c>
+      <x:c r="C37" s="3" t="str">
+        <x:v>27009;6007;3007</x:v>
       </x:c>
       <x:c r="D37" s="3" t="n">
         <x:v>27036</x:v>
@@ -1161,15 +1007,11 @@
       <x:c r="A38" s="2" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B38" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷音大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C38" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27010;6008;3008</x:t>
-        </x:is>
+      <x:c r="B38" s="2" t="str">
+        <x:v>雷音大丹</x:v>
+      </x:c>
+      <x:c r="C38" s="3" t="str">
+        <x:v>27010;6008;3008</x:v>
       </x:c>
       <x:c r="D38" s="3" t="n">
         <x:v>27037</x:v>
@@ -1182,15 +1024,11 @@
       <x:c r="A39" s="2" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B39" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C39" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27011;6009;3009</x:t>
-        </x:is>
+      <x:c r="B39" s="2" t="str">
+        <x:v>地脉大丹</x:v>
+      </x:c>
+      <x:c r="C39" s="3" t="str">
+        <x:v>27011;6009;3009</x:v>
       </x:c>
       <x:c r="D39" s="3" t="n">
         <x:v>27038</x:v>
@@ -1203,15 +1041,11 @@
       <x:c r="A40" s="2" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B40" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星辉大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C40" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27012;6010;3010</x:t>
-        </x:is>
+      <x:c r="B40" s="2" t="str">
+        <x:v>星辉大丹</x:v>
+      </x:c>
+      <x:c r="C40" s="3" t="str">
+        <x:v>27012;6010;3010</x:v>
       </x:c>
       <x:c r="D40" s="3" t="n">
         <x:v>27039</x:v>
@@ -1224,15 +1058,11 @@
       <x:c r="A41" s="2" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B41" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫府大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C41" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27013;6011;3011</x:t>
-        </x:is>
+      <x:c r="B41" s="2" t="str">
+        <x:v>紫府大丹</x:v>
+      </x:c>
+      <x:c r="C41" s="3" t="str">
+        <x:v>27013;6011;3011</x:v>
       </x:c>
       <x:c r="D41" s="3" t="n">
         <x:v>27040</x:v>
@@ -1245,15 +1075,11 @@
       <x:c r="A42" s="2" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B42" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C42" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27014;6012;9012</x:t>
-        </x:is>
+      <x:c r="B42" s="2" t="str">
+        <x:v>九窍大丹</x:v>
+      </x:c>
+      <x:c r="C42" s="3" t="str">
+        <x:v>27014;6012;9012</x:v>
       </x:c>
       <x:c r="D42" s="3" t="n">
         <x:v>27041</x:v>
@@ -1266,15 +1092,11 @@
       <x:c r="A43" s="2" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B43" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅槃大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C43" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27023;6013;3013</x:t>
-        </x:is>
+      <x:c r="B43" s="2" t="str">
+        <x:v>涅槃大丹</x:v>
+      </x:c>
+      <x:c r="C43" s="3" t="str">
+        <x:v>27023;6013;3013</x:v>
       </x:c>
       <x:c r="D43" s="3" t="n">
         <x:v>27042</x:v>
@@ -1287,15 +1109,11 @@
       <x:c r="A44" s="2" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B44" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙灵大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C44" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27024;6014;3014</x:t>
-        </x:is>
+      <x:c r="B44" s="2" t="str">
+        <x:v>龙灵大丹</x:v>
+      </x:c>
+      <x:c r="C44" s="3" t="str">
+        <x:v>27024;6014;3014</x:v>
       </x:c>
       <x:c r="D44" s="3" t="n">
         <x:v>27043</x:v>
@@ -1308,15 +1126,11 @@
       <x:c r="A45" s="2" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B45" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤血大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C45" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27025;6015;3015</x:t>
-        </x:is>
+      <x:c r="B45" s="2" t="str">
+        <x:v>凤血大丹</x:v>
+      </x:c>
+      <x:c r="C45" s="3" t="str">
+        <x:v>27025;6015;3015</x:v>
       </x:c>
       <x:c r="D45" s="3" t="n">
         <x:v>27044</x:v>
@@ -1329,15 +1143,11 @@
       <x:c r="A46" s="2" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B46" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C46" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27026;6016;3016</x:t>
-        </x:is>
+      <x:c r="B46" s="2" t="str">
+        <x:v>混沌大丹</x:v>
+      </x:c>
+      <x:c r="C46" s="3" t="str">
+        <x:v>27026;6016;3016</x:v>
       </x:c>
       <x:c r="D46" s="3" t="n">
         <x:v>27045</x:v>
@@ -1350,15 +1160,11 @@
       <x:c r="A47" s="2" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B47" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九转金丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C47" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27013;27014;27023;3016</x:t>
-        </x:is>
+      <x:c r="B47" s="2" t="str">
+        <x:v>九转金丹</x:v>
+      </x:c>
+      <x:c r="C47" s="3" t="str">
+        <x:v>27013;27014;27023;3016</x:v>
       </x:c>
       <x:c r="D47" s="3" t="n">
         <x:v>27046</x:v>
@@ -1371,15 +1177,11 @@
       <x:c r="A48" s="2" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B48" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太清仙丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C48" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27024;27025;27026;4016</x:t>
-        </x:is>
+      <x:c r="B48" s="2" t="str">
+        <x:v>太清仙丹</x:v>
+      </x:c>
+      <x:c r="C48" s="3" t="str">
+        <x:v>27024;27025;27026;4016</x:v>
       </x:c>
       <x:c r="D48" s="3" t="n">
         <x:v>27047</x:v>
@@ -1392,15 +1194,11 @@
       <x:c r="A49" s="2" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B49" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">天地玄黄丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C49" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27006;27034;27019;27030</x:t>
-        </x:is>
+      <x:c r="B49" s="2" t="str">
+        <x:v>天地玄黄丹</x:v>
+      </x:c>
+      <x:c r="C49" s="3" t="str">
+        <x:v>27006;27034;27019;27030</x:v>
       </x:c>
       <x:c r="D49" s="3" t="n">
         <x:v>27048</x:v>
@@ -1413,15 +1211,11 @@
       <x:c r="A50" s="2" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B50" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">五气朝元丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C50" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27013;27035;27038;27039</x:t>
-        </x:is>
+      <x:c r="B50" s="2" t="str">
+        <x:v>五气朝元丹</x:v>
+      </x:c>
+      <x:c r="C50" s="3" t="str">
+        <x:v>27013;27035;27038;27039</x:v>
       </x:c>
       <x:c r="D50" s="3" t="n">
         <x:v>27049</x:v>
@@ -1434,15 +1228,11 @@
       <x:c r="A51" s="2" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B51" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">万法归宗丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C51" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27045;27047;27046;9016</x:t>
-        </x:is>
+      <x:c r="B51" s="2" t="str">
+        <x:v>万法归宗丹</x:v>
+      </x:c>
+      <x:c r="C51" s="3" t="str">
+        <x:v>27045;27047;27046;9016</x:v>
       </x:c>
       <x:c r="D51" s="3" t="n">
         <x:v>27050</x:v>
@@ -1455,15 +1245,11 @@
       <x:c r="A52" s="2" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B52" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">回灵散</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C52" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9001;3001</x:t>
-        </x:is>
+      <x:c r="B52" s="2" t="str">
+        <x:v>回灵散</x:v>
+      </x:c>
+      <x:c r="C52" s="3" t="str">
+        <x:v>9001;3001</x:v>
       </x:c>
       <x:c r="D52" s="3" t="n">
         <x:v>27051</x:v>
@@ -1476,15 +1262,11 @@
       <x:c r="A53" s="2" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B53" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复灵丸</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C53" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9002;3002</x:t>
-        </x:is>
+      <x:c r="B53" s="2" t="str">
+        <x:v>复灵丸</x:v>
+      </x:c>
+      <x:c r="C53" s="3" t="str">
+        <x:v>9002;3002</x:v>
       </x:c>
       <x:c r="D53" s="3" t="n">
         <x:v>27052</x:v>
@@ -1497,15 +1279,11 @@
       <x:c r="A54" s="2" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B54" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清心露</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C54" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9003;3003</x:t>
-        </x:is>
+      <x:c r="B54" s="2" t="str">
+        <x:v>清心露</x:v>
+      </x:c>
+      <x:c r="C54" s="3" t="str">
+        <x:v>9003;3003</x:v>
       </x:c>
       <x:c r="D54" s="3" t="n">
         <x:v>27053</x:v>
@@ -1518,15 +1296,11 @@
       <x:c r="A55" s="2" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B55" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玉灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C55" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9004;3004;6002</x:t>
-        </x:is>
+      <x:c r="B55" s="2" t="str">
+        <x:v>玉灵丹</x:v>
+      </x:c>
+      <x:c r="C55" s="3" t="str">
+        <x:v>9004;3004;6002</x:v>
       </x:c>
       <x:c r="D55" s="3" t="n">
         <x:v>27054</x:v>
@@ -1539,15 +1313,11 @@
       <x:c r="A56" s="2" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B56" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">冰心丸</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C56" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9005;3005;6005</x:t>
-        </x:is>
+      <x:c r="B56" s="2" t="str">
+        <x:v>冰心丸</x:v>
+      </x:c>
+      <x:c r="C56" s="3" t="str">
+        <x:v>9005;3005;6005</x:v>
       </x:c>
       <x:c r="D56" s="3" t="n">
         <x:v>27055</x:v>
@@ -1560,15 +1330,11 @@
       <x:c r="A57" s="2" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B57" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">火灵散</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C57" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12006;3006;6006</x:t>
-        </x:is>
+      <x:c r="B57" s="2" t="str">
+        <x:v>火灵散</x:v>
+      </x:c>
+      <x:c r="C57" s="3" t="str">
+        <x:v>9006;3006;6006</x:v>
       </x:c>
       <x:c r="D57" s="3" t="n">
         <x:v>27056</x:v>
@@ -1581,15 +1347,11 @@
       <x:c r="A58" s="2" t="n">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B58" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青木露</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C58" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9007;3007;6007</x:t>
-        </x:is>
+      <x:c r="B58" s="2" t="str">
+        <x:v>青木露</x:v>
+      </x:c>
+      <x:c r="C58" s="3" t="str">
+        <x:v>9007;3007;6007</x:v>
       </x:c>
       <x:c r="D58" s="3" t="n">
         <x:v>27057</x:v>
@@ -1602,15 +1364,11 @@
       <x:c r="A59" s="2" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B59" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷光液</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C59" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9008;3008;6008</x:t>
-        </x:is>
+      <x:c r="B59" s="2" t="str">
+        <x:v>雷光液</x:v>
+      </x:c>
+      <x:c r="C59" s="3" t="str">
+        <x:v>9008;3008;6008</x:v>
       </x:c>
       <x:c r="D59" s="3" t="n">
         <x:v>27058</x:v>
@@ -1623,15 +1381,11 @@
       <x:c r="A60" s="2" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B60" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉浆</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C60" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12009;3009;6009</x:t>
-        </x:is>
+      <x:c r="B60" s="2" t="str">
+        <x:v>地脉浆</x:v>
+      </x:c>
+      <x:c r="C60" s="3" t="str">
+        <x:v>9009;3009;6009</x:v>
       </x:c>
       <x:c r="D60" s="3" t="n">
         <x:v>27059</x:v>
@@ -1644,15 +1398,11 @@
       <x:c r="A61" s="2" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B61" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星辉液</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C61" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9010;3010;6010</x:t>
-        </x:is>
+      <x:c r="B61" s="2" t="str">
+        <x:v>星辉液</x:v>
+      </x:c>
+      <x:c r="C61" s="3" t="str">
+        <x:v>9010;3010;6010</x:v>
       </x:c>
       <x:c r="D61" s="3" t="n">
         <x:v>27060</x:v>
@@ -1665,15 +1415,11 @@
       <x:c r="A62" s="2" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B62" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒泉丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C62" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1005;7005;8005;6005</x:t>
-        </x:is>
+      <x:c r="B62" s="2" t="str">
+        <x:v>寒泉丹</x:v>
+      </x:c>
+      <x:c r="C62" s="3" t="str">
+        <x:v>1005;7005;8005;6005</x:v>
       </x:c>
       <x:c r="D62" s="3" t="n">
         <x:v>27061</x:v>
@@ -1686,15 +1432,11 @@
       <x:c r="A63" s="2" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B63" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">炎泉丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C63" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1006;7006;8006;6006</x:t>
-        </x:is>
+      <x:c r="B63" s="2" t="str">
+        <x:v>炎泉丹</x:v>
+      </x:c>
+      <x:c r="C63" s="3" t="str">
+        <x:v>1006;7006;8006;6006</x:v>
       </x:c>
       <x:c r="D63" s="3" t="n">
         <x:v>27062</x:v>
@@ -1707,15 +1449,11 @@
       <x:c r="A64" s="2" t="n">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B64" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青泉丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C64" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1007;7007;8007;6007</x:t>
-        </x:is>
+      <x:c r="B64" s="2" t="str">
+        <x:v>青泉丹</x:v>
+      </x:c>
+      <x:c r="C64" s="3" t="str">
+        <x:v>1007;7007;8007;6007</x:v>
       </x:c>
       <x:c r="D64" s="3" t="n">
         <x:v>27063</x:v>
@@ -1728,15 +1466,11 @@
       <x:c r="A65" s="2" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B65" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷泉丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C65" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1008;7008;8008;6008</x:t>
-        </x:is>
+      <x:c r="B65" s="2" t="str">
+        <x:v>雷泉丹</x:v>
+      </x:c>
+      <x:c r="C65" s="3" t="str">
+        <x:v>1008;7008;8008;6008</x:v>
       </x:c>
       <x:c r="D65" s="3" t="n">
         <x:v>27064</x:v>
@@ -1749,15 +1483,11 @@
       <x:c r="A66" s="2" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B66" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地髓大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C66" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1009;7009;8009;6009</x:t>
-        </x:is>
+      <x:c r="B66" s="2" t="str">
+        <x:v>地髓大丹</x:v>
+      </x:c>
+      <x:c r="C66" s="3" t="str">
+        <x:v>1009;7009;8009;6009</x:v>
       </x:c>
       <x:c r="D66" s="3" t="n">
         <x:v>27065</x:v>
@@ -1770,15 +1500,11 @@
       <x:c r="A67" s="2" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B67" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星尘大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C67" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1010;7010;8010;6010</x:t>
-        </x:is>
+      <x:c r="B67" s="2" t="str">
+        <x:v>星尘大丹</x:v>
+      </x:c>
+      <x:c r="C67" s="3" t="str">
+        <x:v>1010;7010;8010;6010</x:v>
       </x:c>
       <x:c r="D67" s="3" t="n">
         <x:v>27066</x:v>
@@ -1791,15 +1517,11 @@
       <x:c r="A68" s="2" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B68" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫气大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C68" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1011;7011;8011;6011</x:t>
-        </x:is>
+      <x:c r="B68" s="2" t="str">
+        <x:v>紫气大丹</x:v>
+      </x:c>
+      <x:c r="C68" s="3" t="str">
+        <x:v>1011;7011;8011;6011</x:v>
       </x:c>
       <x:c r="D68" s="3" t="n">
         <x:v>27067</x:v>
@@ -1812,15 +1534,11 @@
       <x:c r="A69" s="2" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B69" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九泉大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C69" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1012;7012;8012;6012</x:t>
-        </x:is>
+      <x:c r="B69" s="2" t="str">
+        <x:v>九泉大丹</x:v>
+      </x:c>
+      <x:c r="C69" s="3" t="str">
+        <x:v>1012;7012;8012;6012</x:v>
       </x:c>
       <x:c r="D69" s="3" t="n">
         <x:v>27068</x:v>
@@ -1833,15 +1551,11 @@
       <x:c r="A70" s="2" t="n">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B70" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地皇灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C70" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5009;12009</x:t>
-        </x:is>
+      <x:c r="B70" s="2" t="str">
+        <x:v>地皇灵丹</x:v>
+      </x:c>
+      <x:c r="C70" s="3" t="str">
+        <x:v>5009;9009</x:v>
       </x:c>
       <x:c r="D70" s="3" t="n">
         <x:v>27069</x:v>
@@ -1854,15 +1568,11 @@
       <x:c r="A71" s="2" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B71" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星芒灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C71" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5010;9010</x:t>
-        </x:is>
+      <x:c r="B71" s="2" t="str">
+        <x:v>星芒灵丹</x:v>
+      </x:c>
+      <x:c r="C71" s="3" t="str">
+        <x:v>5010;9010</x:v>
       </x:c>
       <x:c r="D71" s="3" t="n">
         <x:v>27070</x:v>
@@ -1875,15 +1585,11 @@
       <x:c r="A72" s="2" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B72" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫府灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C72" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5011;9011</x:t>
-        </x:is>
+      <x:c r="B72" s="2" t="str">
+        <x:v>紫府灵丹</x:v>
+      </x:c>
+      <x:c r="C72" s="3" t="str">
+        <x:v>5011;9011</x:v>
       </x:c>
       <x:c r="D72" s="3" t="n">
         <x:v>27071</x:v>
@@ -1896,15 +1602,11 @@
       <x:c r="A73" s="2" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B73" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C73" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5012;9012</x:t>
-        </x:is>
+      <x:c r="B73" s="2" t="str">
+        <x:v>九窍灵丹</x:v>
+      </x:c>
+      <x:c r="C73" s="3" t="str">
+        <x:v>5012;9012</x:v>
       </x:c>
       <x:c r="D73" s="3" t="n">
         <x:v>27072</x:v>
@@ -1917,15 +1619,11 @@
       <x:c r="A74" s="2" t="n">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B74" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">麒麟灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C74" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7013;8013;12013</x:t>
-        </x:is>
+      <x:c r="B74" s="2" t="str">
+        <x:v>麒麟灵丹</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="str">
+        <x:v>7013;8013;9013</x:v>
       </x:c>
       <x:c r="D74" s="3" t="n">
         <x:v>27073</x:v>
@@ -1938,15 +1636,11 @@
       <x:c r="A75" s="2" t="n">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B75" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙鳞灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C75" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7014;8014;12014</x:t>
-        </x:is>
+      <x:c r="B75" s="2" t="str">
+        <x:v>龙鳞灵丹</x:v>
+      </x:c>
+      <x:c r="C75" s="3" t="str">
+        <x:v>7014;8014;9014</x:v>
       </x:c>
       <x:c r="D75" s="3" t="n">
         <x:v>27074</x:v>
@@ -1959,15 +1653,11 @@
       <x:c r="A76" s="2" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B76" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤羽灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C76" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7015;8015;9015</x:t>
-        </x:is>
+      <x:c r="B76" s="2" t="str">
+        <x:v>凤羽灵丹</x:v>
+      </x:c>
+      <x:c r="C76" s="3" t="str">
+        <x:v>7015;8015;9015</x:v>
       </x:c>
       <x:c r="D76" s="3" t="n">
         <x:v>27075</x:v>
@@ -1980,15 +1670,11 @@
       <x:c r="A77" s="2" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B77" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C77" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7016;8016;9016</x:t>
-        </x:is>
+      <x:c r="B77" s="2" t="str">
+        <x:v>混沌灵丹</x:v>
+      </x:c>
+      <x:c r="C77" s="3" t="str">
+        <x:v>7016;8016;9016</x:v>
       </x:c>
       <x:c r="D77" s="3" t="n">
         <x:v>27080</x:v>
@@ -2001,15 +1687,11 @@
       <x:c r="A78" s="2" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B78" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅槃灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C78" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5013;6013;3013</x:t>
-        </x:is>
+      <x:c r="B78" s="2" t="str">
+        <x:v>涅槃灵丹</x:v>
+      </x:c>
+      <x:c r="C78" s="3" t="str">
+        <x:v>5013;6013;3013</x:v>
       </x:c>
       <x:c r="D78" s="3" t="n">
         <x:v>27077</x:v>
@@ -2022,15 +1704,11 @@
       <x:c r="A79" s="2" t="n">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B79" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙息灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C79" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5014;6014;3014</x:t>
-        </x:is>
+      <x:c r="B79" s="2" t="str">
+        <x:v>龙息灵丹</x:v>
+      </x:c>
+      <x:c r="C79" s="3" t="str">
+        <x:v>5014;6014;3014</x:v>
       </x:c>
       <x:c r="D79" s="3" t="n">
         <x:v>27078</x:v>
@@ -2043,15 +1721,11 @@
       <x:c r="A80" s="2" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B80" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤血灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C80" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5015;6015;3015</x:t>
-        </x:is>
+      <x:c r="B80" s="2" t="str">
+        <x:v>凤血灵丹</x:v>
+      </x:c>
+      <x:c r="C80" s="3" t="str">
+        <x:v>5015;6015;3015</x:v>
       </x:c>
       <x:c r="D80" s="3" t="n">
         <x:v>27079</x:v>
@@ -2064,15 +1738,11 @@
       <x:c r="A81" s="2" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B81" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C81" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5016;6016;3016</x:t>
-        </x:is>
+      <x:c r="B81" s="2" t="str">
+        <x:v>混沌灵丹</x:v>
+      </x:c>
+      <x:c r="C81" s="3" t="str">
+        <x:v>5016;6016;3016</x:v>
       </x:c>
       <x:c r="D81" s="3" t="n">
         <x:v>27080</x:v>
@@ -2085,15 +1755,11 @@
       <x:c r="A82" s="2" t="n">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B82" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">聚灵大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C82" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27002;3002</x:t>
-        </x:is>
+      <x:c r="B82" s="2" t="str">
+        <x:v>聚灵大丹</x:v>
+      </x:c>
+      <x:c r="C82" s="3" t="str">
+        <x:v>27002;3002</x:v>
       </x:c>
       <x:c r="D82" s="3" t="n">
         <x:v>27081</x:v>
@@ -2106,15 +1772,11 @@
       <x:c r="A83" s="2" t="n">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B83" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玉液大丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C83" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27004;9004;3004</x:t>
-        </x:is>
+      <x:c r="B83" s="2" t="str">
+        <x:v>玉液大丹</x:v>
+      </x:c>
+      <x:c r="C83" s="3" t="str">
+        <x:v>27004;9004;3004</x:v>
       </x:c>
       <x:c r="D83" s="3" t="n">
         <x:v>27082</x:v>
@@ -2127,15 +1789,11 @@
       <x:c r="A84" s="2" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B84" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄冰大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C84" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27005;3005;6005</x:t>
-        </x:is>
+      <x:c r="B84" s="2" t="str">
+        <x:v>玄冰大灵丹</x:v>
+      </x:c>
+      <x:c r="C84" s="3" t="str">
+        <x:v>27005;3005;6005</x:v>
       </x:c>
       <x:c r="D84" s="3" t="n">
         <x:v>27083</x:v>
@@ -2148,15 +1806,11 @@
       <x:c r="A85" s="2" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B85" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">赤阳大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C85" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27008;3006;6006</x:t>
-        </x:is>
+      <x:c r="B85" s="2" t="str">
+        <x:v>赤阳大灵丹</x:v>
+      </x:c>
+      <x:c r="C85" s="3" t="str">
+        <x:v>27008;3006;6006</x:v>
       </x:c>
       <x:c r="D85" s="3" t="n">
         <x:v>27084</x:v>
@@ -2169,15 +1823,11 @@
       <x:c r="A86" s="2" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B86" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青木大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C86" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27009;3007;6007</x:t>
-        </x:is>
+      <x:c r="B86" s="2" t="str">
+        <x:v>青木大灵丹</x:v>
+      </x:c>
+      <x:c r="C86" s="3" t="str">
+        <x:v>27009;3007;6007</x:v>
       </x:c>
       <x:c r="D86" s="3" t="n">
         <x:v>27085</x:v>
@@ -2190,15 +1840,11 @@
       <x:c r="A87" s="2" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B87" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷音大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C87" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27010;3008;6008</x:t>
-        </x:is>
+      <x:c r="B87" s="2" t="str">
+        <x:v>雷音大灵丹</x:v>
+      </x:c>
+      <x:c r="C87" s="3" t="str">
+        <x:v>27010;3008;6008</x:v>
       </x:c>
       <x:c r="D87" s="3" t="n">
         <x:v>27086</x:v>
@@ -2211,15 +1857,11 @@
       <x:c r="A88" s="2" t="n">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B88" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C88" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27011;3009;6009</x:t>
-        </x:is>
+      <x:c r="B88" s="2" t="str">
+        <x:v>地脉大灵丹</x:v>
+      </x:c>
+      <x:c r="C88" s="3" t="str">
+        <x:v>27011;3009;6009</x:v>
       </x:c>
       <x:c r="D88" s="3" t="n">
         <x:v>27087</x:v>
@@ -2232,15 +1874,11 @@
       <x:c r="A89" s="2" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B89" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星辉大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C89" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27012;3010;6010</x:t>
-        </x:is>
+      <x:c r="B89" s="2" t="str">
+        <x:v>星辉大灵丹</x:v>
+      </x:c>
+      <x:c r="C89" s="3" t="str">
+        <x:v>27012;3010;6010</x:v>
       </x:c>
       <x:c r="D89" s="3" t="n">
         <x:v>27088</x:v>
@@ -2253,15 +1891,11 @@
       <x:c r="A90" s="2" t="n">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B90" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫府大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C90" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27013;3011;6011</x:t>
-        </x:is>
+      <x:c r="B90" s="2" t="str">
+        <x:v>紫府大灵丹</x:v>
+      </x:c>
+      <x:c r="C90" s="3" t="str">
+        <x:v>27013;3011;6011</x:v>
       </x:c>
       <x:c r="D90" s="3" t="n">
         <x:v>27089</x:v>
@@ -2274,15 +1908,11 @@
       <x:c r="A91" s="2" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B91" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C91" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27014;9012;6012</x:t>
-        </x:is>
+      <x:c r="B91" s="2" t="str">
+        <x:v>九窍大灵丹</x:v>
+      </x:c>
+      <x:c r="C91" s="3" t="str">
+        <x:v>27014;9012;6012</x:v>
       </x:c>
       <x:c r="D91" s="3" t="n">
         <x:v>27090</x:v>
@@ -2295,15 +1925,11 @@
       <x:c r="A92" s="2" t="n">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B92" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅槃大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C92" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27023;3013;6013</x:t>
-        </x:is>
+      <x:c r="B92" s="2" t="str">
+        <x:v>涅槃大灵丹</x:v>
+      </x:c>
+      <x:c r="C92" s="3" t="str">
+        <x:v>27023;3013;6013</x:v>
       </x:c>
       <x:c r="D92" s="3" t="n">
         <x:v>27091</x:v>
@@ -2316,15 +1942,11 @@
       <x:c r="A93" s="2" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B93" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙灵大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C93" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27024;3014;6014</x:t>
-        </x:is>
+      <x:c r="B93" s="2" t="str">
+        <x:v>龙灵大灵丹</x:v>
+      </x:c>
+      <x:c r="C93" s="3" t="str">
+        <x:v>27024;3014;6014</x:v>
       </x:c>
       <x:c r="D93" s="3" t="n">
         <x:v>27092</x:v>
@@ -2337,15 +1959,11 @@
       <x:c r="A94" s="2" t="n">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B94" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤血大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C94" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27025;3015;6015</x:t>
-        </x:is>
+      <x:c r="B94" s="2" t="str">
+        <x:v>凤血大灵丹</x:v>
+      </x:c>
+      <x:c r="C94" s="3" t="str">
+        <x:v>27025;3015;6015</x:v>
       </x:c>
       <x:c r="D94" s="3" t="n">
         <x:v>27093</x:v>
@@ -2358,15 +1976,11 @@
       <x:c r="A95" s="2" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B95" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌大灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C95" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27026;3016;6016</x:t>
-        </x:is>
+      <x:c r="B95" s="2" t="str">
+        <x:v>混沌大灵丹</x:v>
+      </x:c>
+      <x:c r="C95" s="3" t="str">
+        <x:v>27026;3016;6016</x:v>
       </x:c>
       <x:c r="D95" s="3" t="n">
         <x:v>27094</x:v>
@@ -2379,15 +1993,11 @@
       <x:c r="A96" s="2" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B96" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九转还灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C96" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27082;27087;27090</x:t>
-        </x:is>
+      <x:c r="B96" s="2" t="str">
+        <x:v>九转还灵丹</x:v>
+      </x:c>
+      <x:c r="C96" s="3" t="str">
+        <x:v>27082;27087;27090</x:v>
       </x:c>
       <x:c r="D96" s="3" t="n">
         <x:v>27095</x:v>
@@ -2400,15 +2010,11 @@
       <x:c r="A97" s="2" t="n">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="B97" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太清还灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C97" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27092;27093;27094</x:t>
-        </x:is>
+      <x:c r="B97" s="2" t="str">
+        <x:v>太清还灵丹</x:v>
+      </x:c>
+      <x:c r="C97" s="3" t="str">
+        <x:v>27092;27093;27094</x:v>
       </x:c>
       <x:c r="D97" s="3" t="n">
         <x:v>27096</x:v>
@@ -2421,15 +2027,11 @@
       <x:c r="A98" s="2" t="n">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B98" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">五灵归元丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C98" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27085;27084;27087;27088</x:t>
-        </x:is>
+      <x:c r="B98" s="2" t="str">
+        <x:v>五灵归元丹</x:v>
+      </x:c>
+      <x:c r="C98" s="3" t="str">
+        <x:v>27085;27084;27087;27088</x:v>
       </x:c>
       <x:c r="D98" s="3" t="n">
         <x:v>27097</x:v>
@@ -2442,15 +2044,11 @@
       <x:c r="A99" s="2" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="B99" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">灵气源泉丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C99" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10010;10012;10014;10016</x:t>
-        </x:is>
+      <x:c r="B99" s="2" t="str">
+        <x:v>灵气源泉丹</x:v>
+      </x:c>
+      <x:c r="C99" s="3" t="str">
+        <x:v>10010;10012;10014;10016</x:v>
       </x:c>
       <x:c r="D99" s="3" t="n">
         <x:v>27099</x:v>
@@ -2463,15 +2061,11 @@
       <x:c r="A100" s="2" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B100" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">生生不息丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C100" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27051;27054;27068;27080</x:t>
-        </x:is>
+      <x:c r="B100" s="2" t="str">
+        <x:v>生生不息丹</x:v>
+      </x:c>
+      <x:c r="C100" s="3" t="str">
+        <x:v>27051;27054;27068;27080</x:v>
       </x:c>
       <x:c r="D100" s="3" t="n">
         <x:v>27100</x:v>
@@ -2484,15 +2078,11 @@
       <x:c r="A101" s="2" t="n">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B101" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">黄粱米酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C101" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5001;9001</x:t>
-        </x:is>
+      <x:c r="B101" s="2" t="str">
+        <x:v>黄粱米酒</x:v>
+      </x:c>
+      <x:c r="C101" s="3" t="str">
+        <x:v>5001;9001</x:v>
       </x:c>
       <x:c r="D101" s="3" t="n">
         <x:v>27101</x:v>
@@ -2505,15 +2095,11 @@
       <x:c r="A102" s="2" t="n">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="B102" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清溪果酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C102" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6002;9002</x:t>
-        </x:is>
+      <x:c r="B102" s="2" t="str">
+        <x:v>清溪果酿</x:v>
+      </x:c>
+      <x:c r="C102" s="3" t="str">
+        <x:v>6002;9002</x:v>
       </x:c>
       <x:c r="D102" s="3" t="n">
         <x:v>27102</x:v>
@@ -2526,15 +2112,11 @@
       <x:c r="A103" s="2" t="n">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B103" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">百花醉</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C103" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3002;9003</x:t>
-        </x:is>
+      <x:c r="B103" s="2" t="str">
+        <x:v>百花醉</x:v>
+      </x:c>
+      <x:c r="C103" s="3" t="str">
+        <x:v>3002;9003</x:v>
       </x:c>
       <x:c r="D103" s="3" t="n">
         <x:v>27103</x:v>
@@ -2547,15 +2129,11 @@
       <x:c r="A104" s="2" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="B104" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玉露琼浆</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C104" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9004;6004</x:t>
-        </x:is>
+      <x:c r="B104" s="2" t="str">
+        <x:v>玉露琼浆</x:v>
+      </x:c>
+      <x:c r="C104" s="3" t="str">
+        <x:v>9004;6004</x:v>
       </x:c>
       <x:c r="D104" s="3" t="n">
         <x:v>27104</x:v>
@@ -2568,15 +2146,11 @@
       <x:c r="A105" s="2" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="B105" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青芽酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C105" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5003;3003;6003</x:t>
-        </x:is>
+      <x:c r="B105" s="2" t="str">
+        <x:v>青芽酿</x:v>
+      </x:c>
+      <x:c r="C105" s="3" t="str">
+        <x:v>5003;3003;6003</x:v>
       </x:c>
       <x:c r="D105" s="3" t="n">
         <x:v>27105</x:v>
@@ -2589,15 +2163,11 @@
       <x:c r="A106" s="2" t="n">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="B106" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">霜华酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C106" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5005;3005;6005</x:t>
-        </x:is>
+      <x:c r="B106" s="2" t="str">
+        <x:v>霜华酿</x:v>
+      </x:c>
+      <x:c r="C106" s="3" t="str">
+        <x:v>5005;3005;6005</x:v>
       </x:c>
       <x:c r="D106" s="3" t="n">
         <x:v>27106</x:v>
@@ -2610,15 +2180,11 @@
       <x:c r="A107" s="2" t="n">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="B107" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">赤阳烧</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C107" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5006;3006;6006</x:t>
-        </x:is>
+      <x:c r="B107" s="2" t="str">
+        <x:v>赤阳烧</x:v>
+      </x:c>
+      <x:c r="C107" s="3" t="str">
+        <x:v>5006;3006;6006</x:v>
       </x:c>
       <x:c r="D107" s="3" t="n">
         <x:v>27107</x:v>
@@ -2631,15 +2197,11 @@
       <x:c r="A108" s="2" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="B108" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青玄酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C108" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5007;3007;6007</x:t>
-        </x:is>
+      <x:c r="B108" s="2" t="str">
+        <x:v>青玄酿</x:v>
+      </x:c>
+      <x:c r="C108" s="3" t="str">
+        <x:v>5007;3007;6007</x:v>
       </x:c>
       <x:c r="D108" s="3" t="n">
         <x:v>27108</x:v>
@@ -2652,15 +2214,11 @@
       <x:c r="A109" s="2" t="n">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B109" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷火酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C109" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5008;3008;6008</x:t>
-        </x:is>
+      <x:c r="B109" s="2" t="str">
+        <x:v>雷火酒</x:v>
+      </x:c>
+      <x:c r="C109" s="3" t="str">
+        <x:v>5008;3008;6008</x:v>
       </x:c>
       <x:c r="D109" s="3" t="n">
         <x:v>27109</x:v>
@@ -2673,15 +2231,11 @@
       <x:c r="A110" s="2" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B110" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉醇</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C110" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5009;3009;6009</x:t>
-        </x:is>
+      <x:c r="B110" s="2" t="str">
+        <x:v>地脉醇</x:v>
+      </x:c>
+      <x:c r="C110" s="3" t="str">
+        <x:v>5009;3009;6009</x:v>
       </x:c>
       <x:c r="D110" s="3" t="n">
         <x:v>27110</x:v>
@@ -2694,15 +2248,11 @@
       <x:c r="A111" s="2" t="n">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B111" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星芒醉</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C111" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5010;3010;6010</x:t>
-        </x:is>
+      <x:c r="B111" s="2" t="str">
+        <x:v>星芒醉</x:v>
+      </x:c>
+      <x:c r="C111" s="3" t="str">
+        <x:v>5010;3010;6010</x:v>
       </x:c>
       <x:c r="D111" s="3" t="n">
         <x:v>27111</x:v>
@@ -2715,15 +2265,11 @@
       <x:c r="A112" s="2" t="n">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B112" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫府仙酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C112" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5011;3011;6011</x:t>
-        </x:is>
+      <x:c r="B112" s="2" t="str">
+        <x:v>紫府仙酿</x:v>
+      </x:c>
+      <x:c r="C112" s="3" t="str">
+        <x:v>5011;3011;6011</x:v>
       </x:c>
       <x:c r="D112" s="3" t="n">
         <x:v>27112</x:v>
@@ -2736,15 +2282,11 @@
       <x:c r="A113" s="2" t="n">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B113" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九孔玉液酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C113" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5012;9012;6012</x:t>
-        </x:is>
+      <x:c r="B113" s="2" t="str">
+        <x:v>九孔玉液酒</x:v>
+      </x:c>
+      <x:c r="C113" s="3" t="str">
+        <x:v>5012;9012;6012</x:v>
       </x:c>
       <x:c r="D113" s="3" t="n">
         <x:v>27113</x:v>
@@ -2757,15 +2299,11 @@
       <x:c r="A114" s="2" t="n">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="B114" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅槃重生酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C114" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5013;3013;6013</x:t>
-        </x:is>
+      <x:c r="B114" s="2" t="str">
+        <x:v>涅槃重生酿</x:v>
+      </x:c>
+      <x:c r="C114" s="3" t="str">
+        <x:v>5013;3013;6013</x:v>
       </x:c>
       <x:c r="D114" s="3" t="n">
         <x:v>27114</x:v>
@@ -2778,15 +2316,11 @@
       <x:c r="A115" s="2" t="n">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B115" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙息醇</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C115" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5014;3014;6014</x:t>
-        </x:is>
+      <x:c r="B115" s="2" t="str">
+        <x:v>龙息醇</x:v>
+      </x:c>
+      <x:c r="C115" s="3" t="str">
+        <x:v>5014;3014;6014</x:v>
       </x:c>
       <x:c r="D115" s="3" t="n">
         <x:v>27115</x:v>
@@ -2799,15 +2333,11 @@
       <x:c r="A116" s="2" t="n">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B116" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤羽天酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C116" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5015;3015;6015</x:t>
-        </x:is>
+      <x:c r="B116" s="2" t="str">
+        <x:v>凤羽天酿</x:v>
+      </x:c>
+      <x:c r="C116" s="3" t="str">
+        <x:v>5015;3015;6015</x:v>
       </x:c>
       <x:c r="D116" s="3" t="n">
         <x:v>27116</x:v>
@@ -2820,15 +2350,11 @@
       <x:c r="A117" s="2" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="B117" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌元酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C117" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5016;3016;6016</x:t>
-        </x:is>
+      <x:c r="B117" s="2" t="str">
+        <x:v>混沌元酒</x:v>
+      </x:c>
+      <x:c r="C117" s="3" t="str">
+        <x:v>5016;3016;6016</x:v>
       </x:c>
       <x:c r="D117" s="3" t="n">
         <x:v>27117</x:v>
@@ -2841,15 +2367,11 @@
       <x:c r="A118" s="2" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="B118" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">冰蚕寒酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C118" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7005;3005;1005</x:t>
-        </x:is>
+      <x:c r="B118" s="2" t="str">
+        <x:v>冰蚕寒酿</x:v>
+      </x:c>
+      <x:c r="C118" s="3" t="str">
+        <x:v>7005;3005;1005</x:v>
       </x:c>
       <x:c r="D118" s="3" t="n">
         <x:v>27118</x:v>
@@ -2862,15 +2384,11 @@
       <x:c r="A119" s="2" t="n">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="B119" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">火浣烈酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C119" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7006;3006;1006</x:t>
-        </x:is>
+      <x:c r="B119" s="2" t="str">
+        <x:v>火浣烈酒</x:v>
+      </x:c>
+      <x:c r="C119" s="3" t="str">
+        <x:v>7006;3006;1006</x:v>
       </x:c>
       <x:c r="D119" s="3" t="n">
         <x:v>27119</x:v>
@@ -2883,15 +2401,11 @@
       <x:c r="A120" s="2" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B120" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟甲养身酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C120" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7007;3007;1007</x:t>
-        </x:is>
+      <x:c r="B120" s="2" t="str">
+        <x:v>龟甲养身酒</x:v>
+      </x:c>
+      <x:c r="C120" s="3" t="str">
+        <x:v>7007;3007;1007</x:v>
       </x:c>
       <x:c r="D120" s="3" t="n">
         <x:v>27120</x:v>
@@ -2904,15 +2418,11 @@
       <x:c r="A121" s="2" t="n">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B121" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷蟒电光酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C121" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7008;3008;1008</x:t>
-        </x:is>
+      <x:c r="B121" s="2" t="str">
+        <x:v>雷蟒电光酒</x:v>
+      </x:c>
+      <x:c r="C121" s="3" t="str">
+        <x:v>7008;3008;1008</x:v>
       </x:c>
       <x:c r="D121" s="3" t="n">
         <x:v>27121</x:v>
@@ -2925,15 +2435,11 @@
       <x:c r="A122" s="2" t="n">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B122" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地龙沉酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C122" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7009;3009;1009</x:t>
-        </x:is>
+      <x:c r="B122" s="2" t="str">
+        <x:v>地龙沉酿</x:v>
+      </x:c>
+      <x:c r="C122" s="3" t="str">
+        <x:v>7009;3009;1009</x:v>
       </x:c>
       <x:c r="D122" s="3" t="n">
         <x:v>27122</x:v>
@@ -2946,15 +2452,11 @@
       <x:c r="A123" s="2" t="n">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="B123" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星貂幻酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C123" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7010;3010;1010</x:t>
-        </x:is>
+      <x:c r="B123" s="2" t="str">
+        <x:v>星貂幻酒</x:v>
+      </x:c>
+      <x:c r="C123" s="3" t="str">
+        <x:v>7010;3010;1010</x:v>
       </x:c>
       <x:c r="D123" s="3" t="n">
         <x:v>27123</x:v>
@@ -2967,15 +2469,11 @@
       <x:c r="A124" s="2" t="n">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="B124" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫狐迷魂酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C124" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7011;3011;1011</x:t>
-        </x:is>
+      <x:c r="B124" s="2" t="str">
+        <x:v>紫狐迷魂酒</x:v>
+      </x:c>
+      <x:c r="C124" s="3" t="str">
+        <x:v>7011;3011;1011</x:v>
       </x:c>
       <x:c r="D124" s="3" t="n">
         <x:v>27124</x:v>
@@ -2988,15 +2486,11 @@
       <x:c r="A125" s="2" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="B125" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九尾灵酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C125" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7012;9012;1012</x:t>
-        </x:is>
+      <x:c r="B125" s="2" t="str">
+        <x:v>九尾灵酒</x:v>
+      </x:c>
+      <x:c r="C125" s="3" t="str">
+        <x:v>7012;9012;1012</x:v>
       </x:c>
       <x:c r="D125" s="3" t="n">
         <x:v>27125</x:v>
@@ -3009,15 +2503,11 @@
       <x:c r="A126" s="2" t="n">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B126" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">麒麟祥瑞酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C126" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7013;12013;8013</x:t>
-        </x:is>
+      <x:c r="B126" s="2" t="str">
+        <x:v>麒麟祥瑞酒</x:v>
+      </x:c>
+      <x:c r="C126" s="3" t="str">
+        <x:v>7013;9013;8013</x:v>
       </x:c>
       <x:c r="D126" s="3" t="n">
         <x:v>27126</x:v>
@@ -3030,15 +2520,11 @@
       <x:c r="A127" s="2" t="n">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B127" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙鳞战酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C127" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7014;12014;8014</x:t>
-        </x:is>
+      <x:c r="B127" s="2" t="str">
+        <x:v>龙鳞战酒</x:v>
+      </x:c>
+      <x:c r="C127" s="3" t="str">
+        <x:v>7014;9014;8014</x:v>
       </x:c>
       <x:c r="D127" s="3" t="n">
         <x:v>27127</x:v>
@@ -3051,15 +2537,11 @@
       <x:c r="A128" s="2" t="n">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B128" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤羽涅槃酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C128" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7015;9015;8015</x:t>
-        </x:is>
+      <x:c r="B128" s="2" t="str">
+        <x:v>凤羽涅槃酒</x:v>
+      </x:c>
+      <x:c r="C128" s="3" t="str">
+        <x:v>7015;9015;8015</x:v>
       </x:c>
       <x:c r="D128" s="3" t="n">
         <x:v>27128</x:v>
@@ -3072,15 +2554,11 @@
       <x:c r="A129" s="2" t="n">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B129" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌悟道酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C129" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7016;9016;8016</x:t>
-        </x:is>
+      <x:c r="B129" s="2" t="str">
+        <x:v>混沌悟道酒</x:v>
+      </x:c>
+      <x:c r="C129" s="3" t="str">
+        <x:v>7016;9016;8016</x:v>
       </x:c>
       <x:c r="D129" s="3" t="n">
         <x:v>27129</x:v>
@@ -3093,15 +2571,11 @@
       <x:c r="A130" s="2" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="B130" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">灵果甘酿</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C130" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6004;9004;3004</x:t>
-        </x:is>
+      <x:c r="B130" s="2" t="str">
+        <x:v>灵果甘酿</x:v>
+      </x:c>
+      <x:c r="C130" s="3" t="str">
+        <x:v>6004;9004;3004</x:v>
       </x:c>
       <x:c r="D130" s="3" t="n">
         <x:v>27130</x:v>
@@ -3114,15 +2588,11 @@
       <x:c r="A131" s="2" t="n">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B131" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉灵根酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C131" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6009;12009;3009</x:t>
-        </x:is>
+      <x:c r="B131" s="2" t="str">
+        <x:v>地脉灵根酒</x:v>
+      </x:c>
+      <x:c r="C131" s="3" t="str">
+        <x:v>6009;9009;3009</x:v>
       </x:c>
       <x:c r="D131" s="3" t="n">
         <x:v>27131</x:v>
@@ -3135,15 +2605,11 @@
       <x:c r="A132" s="2" t="n">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="B132" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星辉甘霖酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C132" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6010;9010;3010</x:t>
-        </x:is>
+      <x:c r="B132" s="2" t="str">
+        <x:v>星辉甘霖酒</x:v>
+      </x:c>
+      <x:c r="C132" s="3" t="str">
+        <x:v>6010;9010;3010</x:v>
       </x:c>
       <x:c r="D132" s="3" t="n">
         <x:v>27132</x:v>
@@ -3156,15 +2622,11 @@
       <x:c r="A133" s="2" t="n">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="B133" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">紫光仙酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C133" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6011;9011;3011</x:t>
-        </x:is>
+      <x:c r="B133" s="2" t="str">
+        <x:v>紫光仙酒</x:v>
+      </x:c>
+      <x:c r="C133" s="3" t="str">
+        <x:v>6011;9011;3011</x:v>
       </x:c>
       <x:c r="D133" s="3" t="n">
         <x:v>27133</x:v>
@@ -3177,15 +2639,11 @@
       <x:c r="A134" s="2" t="n">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="B134" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九窍玉髓酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C134" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6012;9012;5012</x:t>
-        </x:is>
+      <x:c r="B134" s="2" t="str">
+        <x:v>九窍玉髓酒</x:v>
+      </x:c>
+      <x:c r="C134" s="3" t="str">
+        <x:v>6012;9012;5012</x:v>
       </x:c>
       <x:c r="D134" s="3" t="n">
         <x:v>27134</x:v>
@@ -3198,15 +2656,11 @@
       <x:c r="A135" s="2" t="n">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="B135" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅槃烈酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C135" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6013;12013;3013</x:t>
-        </x:is>
+      <x:c r="B135" s="2" t="str">
+        <x:v>涅槃烈酒</x:v>
+      </x:c>
+      <x:c r="C135" s="3" t="str">
+        <x:v>6013;9013;3013</x:v>
       </x:c>
       <x:c r="D135" s="3" t="n">
         <x:v>27135</x:v>
@@ -3219,15 +2673,11 @@
       <x:c r="A136" s="2" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="B136" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙涎封侯酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C136" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6014;12014;3014</x:t>
-        </x:is>
+      <x:c r="B136" s="2" t="str">
+        <x:v>龙涎封侯酒</x:v>
+      </x:c>
+      <x:c r="C136" s="3" t="str">
+        <x:v>6014;9014;3014</x:v>
       </x:c>
       <x:c r="D136" s="3" t="n">
         <x:v>27136</x:v>
@@ -3240,15 +2690,11 @@
       <x:c r="A137" s="2" t="n">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="B137" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤羽飞天酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C137" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6015;9015;3015</x:t>
-        </x:is>
+      <x:c r="B137" s="2" t="str">
+        <x:v>凤羽飞天酒</x:v>
+      </x:c>
+      <x:c r="C137" s="3" t="str">
+        <x:v>6015;9015;3015</x:v>
       </x:c>
       <x:c r="D137" s="3" t="n">
         <x:v>27137</x:v>
@@ -3261,15 +2707,11 @@
       <x:c r="A138" s="2" t="n">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="B138" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌朝圣酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C138" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6016;9016;3016</x:t>
-        </x:is>
+      <x:c r="B138" s="2" t="str">
+        <x:v>混沌朝圣酒</x:v>
+      </x:c>
+      <x:c r="C138" s="3" t="str">
+        <x:v>6016;9016;3016</x:v>
       </x:c>
       <x:c r="D138" s="3" t="n">
         <x:v>27138</x:v>
@@ -3282,15 +2724,11 @@
       <x:c r="A139" s="2" t="n">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="B139" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒泉冻骨酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C139" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9005;1005;3005</x:t>
-        </x:is>
+      <x:c r="B139" s="2" t="str">
+        <x:v>寒泉冻骨酒</x:v>
+      </x:c>
+      <x:c r="C139" s="3" t="str">
+        <x:v>9005;1005;3005</x:v>
       </x:c>
       <x:c r="D139" s="3" t="n">
         <x:v>27139</x:v>
@@ -3303,15 +2741,11 @@
       <x:c r="A140" s="2" t="n">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="B140" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">炎泉沸血酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C140" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12006;1006;3006</x:t>
-        </x:is>
+      <x:c r="B140" s="2" t="str">
+        <x:v>炎泉沸血酒</x:v>
+      </x:c>
+      <x:c r="C140" s="3" t="str">
+        <x:v>9006;1006;3006</x:v>
       </x:c>
       <x:c r="D140" s="3" t="n">
         <x:v>27140</x:v>
@@ -3324,15 +2758,11 @@
       <x:c r="A141" s="2" t="n">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="B141" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青泉生机酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C141" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9007;1007;3007</x:t>
-        </x:is>
+      <x:c r="B141" s="2" t="str">
+        <x:v>青泉生机酒</x:v>
+      </x:c>
+      <x:c r="C141" s="3" t="str">
+        <x:v>9007;1007;3007</x:v>
       </x:c>
       <x:c r="D141" s="3" t="n">
         <x:v>27141</x:v>
@@ -3345,15 +2775,11 @@
       <x:c r="A142" s="2" t="n">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="B142" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雷泉电身酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C142" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9008;1008;3008</x:t>
-        </x:is>
+      <x:c r="B142" s="2" t="str">
+        <x:v>雷泉电身酒</x:v>
+      </x:c>
+      <x:c r="C142" s="3" t="str">
+        <x:v>9008;1008;3008</x:v>
       </x:c>
       <x:c r="D142" s="3" t="n">
         <x:v>27142</x:v>
@@ -3366,15 +2792,11 @@
       <x:c r="A143" s="2" t="n">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="B143" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九转回春酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C143" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27051;27054;27068</x:t>
-        </x:is>
+      <x:c r="B143" s="2" t="str">
+        <x:v>九转回春酒</x:v>
+      </x:c>
+      <x:c r="C143" s="3" t="str">
+        <x:v>27051;27054;27068</x:v>
       </x:c>
       <x:c r="D143" s="3" t="n">
         <x:v>27143</x:v>
@@ -3387,15 +2809,11 @@
       <x:c r="A144" s="2" t="n">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="B144" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">百草灵酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C144" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1001;1002;1003;9004</x:t>
-        </x:is>
+      <x:c r="B144" s="2" t="str">
+        <x:v>百草灵酒</x:v>
+      </x:c>
+      <x:c r="C144" s="3" t="str">
+        <x:v>1001;1002;1003;9004</x:v>
       </x:c>
       <x:c r="D144" s="3" t="n">
         <x:v>27144</x:v>
@@ -3408,15 +2826,11 @@
       <x:c r="A145" s="2" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="B145" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">五灵合酿酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C145" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27108;27107;27110;27111</x:t>
-        </x:is>
+      <x:c r="B145" s="2" t="str">
+        <x:v>五灵合酿酒</x:v>
+      </x:c>
+      <x:c r="C145" s="3" t="str">
+        <x:v>27108;27107;27110;27111</x:v>
       </x:c>
       <x:c r="D145" s="3" t="n">
         <x:v>27145</x:v>
@@ -3429,15 +2843,11 @@
       <x:c r="A146" s="2" t="n">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="B146" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">三花聚顶酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C146" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3002;3007;3011</x:t>
-        </x:is>
+      <x:c r="B146" s="2" t="str">
+        <x:v>三花聚顶酒</x:v>
+      </x:c>
+      <x:c r="C146" s="3" t="str">
+        <x:v>3002;3007;3011</x:v>
       </x:c>
       <x:c r="D146" s="3" t="n">
         <x:v>27146</x:v>
@@ -3450,15 +2860,11 @@
       <x:c r="A147" s="2" t="n">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B147" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">五行调和酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C147" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27118;27119;27120;27121</x:t>
-        </x:is>
+      <x:c r="B147" s="2" t="str">
+        <x:v>五行调和酒</x:v>
+      </x:c>
+      <x:c r="C147" s="3" t="str">
+        <x:v>27118;27119;27120;27121</x:v>
       </x:c>
       <x:c r="D147" s="3" t="n">
         <x:v>27147</x:v>
@@ -3471,15 +2877,11 @@
       <x:c r="A148" s="2" t="n">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="B148" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九龙升天酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C148" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27115;27127;27136;5014</x:t>
-        </x:is>
+      <x:c r="B148" s="2" t="str">
+        <x:v>九龙升天酒</x:v>
+      </x:c>
+      <x:c r="C148" s="3" t="str">
+        <x:v>27115;27127;27136;5014</x:v>
       </x:c>
       <x:c r="D148" s="3" t="n">
         <x:v>27148</x:v>
@@ -3492,15 +2894,11 @@
       <x:c r="A149" s="2" t="n">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="B149" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九凤朝凰酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C149" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27116;27128;27137;5015</x:t>
-        </x:is>
+      <x:c r="B149" s="2" t="str">
+        <x:v>九凤朝凰酒</x:v>
+      </x:c>
+      <x:c r="C149" s="3" t="str">
+        <x:v>27116;27128;27137;5015</x:v>
       </x:c>
       <x:c r="D149" s="3" t="n">
         <x:v>27149</x:v>
@@ -3513,15 +2911,11 @@
       <x:c r="A150" s="2" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B150" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌万道酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C150" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">27117;27129;27138;5016</x:t>
-        </x:is>
+      <x:c r="B150" s="2" t="str">
+        <x:v>混沌万道酒</x:v>
+      </x:c>
+      <x:c r="C150" s="3" t="str">
+        <x:v>27117;27129;27138;5016</x:v>
       </x:c>
       <x:c r="D150" s="3" t="n">
         <x:v>27150</x:v>
@@ -3534,15 +2928,11 @@
       <x:c r="A151" s="2" t="n">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="B151" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">铁木剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C151" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2002;9001</x:t>
-        </x:is>
+      <x:c r="B151" s="2" t="str">
+        <x:v>铁木剑</x:v>
+      </x:c>
+      <x:c r="C151" s="3" t="str">
+        <x:v>2002;9001</x:v>
       </x:c>
       <x:c r="D151" s="3" t="n">
         <x:v>28001</x:v>
@@ -3555,15 +2945,11 @@
       <x:c r="A152" s="2" t="n">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="B152" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">铜锋剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C152" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2003;9002;4001</x:t>
-        </x:is>
+      <x:c r="B152" s="2" t="str">
+        <x:v>铜锋剑</x:v>
+      </x:c>
+      <x:c r="C152" s="3" t="str">
+        <x:v>2003;9002;4001</x:v>
       </x:c>
       <x:c r="D152" s="3" t="n">
         <x:v>28002</x:v>
@@ -3576,15 +2962,11 @@
       <x:c r="A153" s="2" t="n">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="B153" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">银光剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C153" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2003;2004;4003;9003</x:t>
-        </x:is>
+      <x:c r="B153" s="2" t="str">
+        <x:v>银光剑</x:v>
+      </x:c>
+      <x:c r="C153" s="3" t="str">
+        <x:v>2003;2004;4003;9003</x:v>
       </x:c>
       <x:c r="D153" s="3" t="n">
         <x:v>28003</x:v>
@@ -3597,15 +2979,11 @@
       <x:c r="A154" s="2" t="n">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="B154" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玄金短剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C154" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2004;4004;9004</x:t>
-        </x:is>
+      <x:c r="B154" s="2" t="str">
+        <x:v>玄金短剑</x:v>
+      </x:c>
+      <x:c r="C154" s="3" t="str">
+        <x:v>2004;4004;9004</x:v>
       </x:c>
       <x:c r="D154" s="3" t="n">
         <x:v>28004</x:v>
@@ -3618,15 +2996,11 @@
       <x:c r="A155" s="2" t="n">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="B155" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">寒渊冰剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C155" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2005;4005;9005;4002</x:t>
-        </x:is>
+      <x:c r="B155" s="2" t="str">
+        <x:v>寒渊冰剑</x:v>
+      </x:c>
+      <x:c r="C155" s="3" t="str">
+        <x:v>2005;4005;9005;4002</x:v>
       </x:c>
       <x:c r="D155" s="3" t="n">
         <x:v>28005</x:v>
@@ -3639,15 +3013,11 @@
       <x:c r="A156" s="2" t="n">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="B156" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">赤炎火剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C156" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2006;4006;9006</x:t>
-        </x:is>
+      <x:c r="B156" s="2" t="str">
+        <x:v>赤炎火剑</x:v>
+      </x:c>
+      <x:c r="C156" s="3" t="str">
+        <x:v>2006;4006;9006</x:v>
       </x:c>
       <x:c r="D156" s="3" t="n">
         <x:v>28006</x:v>
@@ -3660,15 +3030,11 @@
       <x:c r="A157" s="2" t="n">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="B157" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青灵木剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C157" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2007;4007;9007;3007</x:t>
-        </x:is>
+      <x:c r="B157" s="2" t="str">
+        <x:v>青灵木剑</x:v>
+      </x:c>
+      <x:c r="C157" s="3" t="str">
+        <x:v>2007;4007;9007;3007</x:v>
       </x:c>
       <x:c r="D157" s="3" t="n">
         <x:v>28007</x:v>
@@ -3681,15 +3047,11 @@
       <x:c r="A158" s="2" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="B158" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">金雷斩邪剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C158" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2008;4008;9008;3008</x:t>
-        </x:is>
+      <x:c r="B158" s="2" t="str">
+        <x:v>金雷斩邪剑</x:v>
+      </x:c>
+      <x:c r="C158" s="3" t="str">
+        <x:v>2008;4008;9008;3008</x:v>
       </x:c>
       <x:c r="D158" s="3" t="n">
         <x:v>28008</x:v>
@@ -3702,15 +3064,11 @@
       <x:c r="A159" s="2" t="n">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="B159" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉重剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C159" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2009;4009;9009;3009</x:t>
-        </x:is>
+      <x:c r="B159" s="2" t="str">
+        <x:v>地脉重剑</x:v>
+      </x:c>
+      <x:c r="C159" s="3" t="str">
+        <x:v>2009;4009;9009;3009</x:v>
       </x:c>
       <x:c r="D159" s="3" t="n">
         <x:v>28009</x:v>
@@ -3723,15 +3081,11 @@
       <x:c r="A160" s="2" t="n">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="B160" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星陨长剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C160" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2010;4010;27060;3010</x:t>
-        </x:is>
+      <x:c r="B160" s="2" t="str">
+        <x:v>星陨长剑</x:v>
+      </x:c>
+      <x:c r="C160" s="3" t="str">
+        <x:v>2010;4010;27060;3010</x:v>
       </x:c>
       <x:c r="D160" s="3" t="n">
         <x:v>28010</x:v>
@@ -3744,15 +3098,11 @@
       <x:c r="A161" s="2" t="n">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="B161" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">虚空影剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C161" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2011;4011;9011;3011</x:t>
-        </x:is>
+      <x:c r="B161" s="2" t="str">
+        <x:v>虚空影剑</x:v>
+      </x:c>
+      <x:c r="C161" s="3" t="str">
+        <x:v>2011;4011;9011;3011</x:v>
       </x:c>
       <x:c r="D161" s="3" t="n">
         <x:v>28011</x:v>
@@ -3765,15 +3115,11 @@
       <x:c r="A162" s="2" t="n">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B162" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九幽玄冥剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C162" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2012;4012;9012;6012</x:t>
-        </x:is>
+      <x:c r="B162" s="2" t="str">
+        <x:v>九幽玄冥剑</x:v>
+      </x:c>
+      <x:c r="C162" s="3" t="str">
+        <x:v>2012;4012;9012;6012</x:v>
       </x:c>
       <x:c r="D162" s="3" t="n">
         <x:v>28012</x:v>
@@ -3786,15 +3132,11 @@
       <x:c r="A163" s="2" t="n">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="B163" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太阳真光剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C163" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2013;4013;9013;3013</x:t>
-        </x:is>
+      <x:c r="B163" s="2" t="str">
+        <x:v>太阳真光剑</x:v>
+      </x:c>
+      <x:c r="C163" s="3" t="str">
+        <x:v>2013;4013;9013;3013</x:v>
       </x:c>
       <x:c r="D163" s="3" t="n">
         <x:v>28013</x:v>
@@ -3807,15 +3149,11 @@
       <x:c r="A164" s="2" t="n">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="B164" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">太阴寒月剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C164" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2014;4014;9014;3014</x:t>
-        </x:is>
+      <x:c r="B164" s="2" t="str">
+        <x:v>太阴寒月剑</x:v>
+      </x:c>
+      <x:c r="C164" s="3" t="str">
+        <x:v>2014;4014;9014;3014</x:v>
       </x:c>
       <x:c r="D164" s="3" t="n">
         <x:v>28014</x:v>
@@ -3828,15 +3166,11 @@
       <x:c r="A165" s="2" t="n">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="B165" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星河无极剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C165" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2015;4015;9015;3015</x:t>
-        </x:is>
+      <x:c r="B165" s="2" t="str">
+        <x:v>星河无极剑</x:v>
+      </x:c>
+      <x:c r="C165" s="3" t="str">
+        <x:v>2015;4015;9015;3015</x:v>
       </x:c>
       <x:c r="D165" s="3" t="n">
         <x:v>28015</x:v>
@@ -3849,15 +3183,11 @@
       <x:c r="A166" s="2" t="n">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="B166" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鸿蒙开天剑</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C166" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2016;4016;9016;3016</x:t>
-        </x:is>
+      <x:c r="B166" s="2" t="str">
+        <x:v>鸿蒙开天剑</x:v>
+      </x:c>
+      <x:c r="C166" s="3" t="str">
+        <x:v>2016;4016;9016;3016</x:v>
       </x:c>
       <x:c r="D166" s="3" t="n">
         <x:v>28016</x:v>
@@ -3870,15 +3200,11 @@
       <x:c r="A167" s="2" t="n">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="B167" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">清风阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C167" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13101;7001;9001</x:t>
-        </x:is>
+      <x:c r="B167" s="2" t="str">
+        <x:v>清风阵</x:v>
+      </x:c>
+      <x:c r="C167" s="3" t="str">
+        <x:v>13101;7001;9001</x:v>
       </x:c>
       <x:c r="D167" s="3" t="n">
         <x:v>28017</x:v>
@@ -3891,15 +3217,11 @@
       <x:c r="A168" s="2" t="n">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="B168" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">聚灵阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C168" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13102;7002;9002;4001</x:t>
-        </x:is>
+      <x:c r="B168" s="2" t="str">
+        <x:v>聚灵阵</x:v>
+      </x:c>
+      <x:c r="C168" s="3" t="str">
+        <x:v>13102;7002;9002;4001</x:v>
       </x:c>
       <x:c r="D168" s="3" t="n">
         <x:v>28018</x:v>
@@ -3912,15 +3234,11 @@
       <x:c r="A169" s="2" t="n">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="B169" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">铁壁阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C169" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13103;7003;4002;9003</x:t>
-        </x:is>
+      <x:c r="B169" s="2" t="str">
+        <x:v>铁壁阵</x:v>
+      </x:c>
+      <x:c r="C169" s="3" t="str">
+        <x:v>13103;7003;4002;9003</x:v>
       </x:c>
       <x:c r="D169" s="3" t="n">
         <x:v>28019</x:v>
@@ -3933,15 +3251,11 @@
       <x:c r="A170" s="2" t="n">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="B170" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">三才锁灵阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C170" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13104;7004;4004;9004</x:t>
-        </x:is>
+      <x:c r="B170" s="2" t="str">
+        <x:v>三才锁灵阵</x:v>
+      </x:c>
+      <x:c r="C170" s="3" t="str">
+        <x:v>13104;7004;4004;9004</x:v>
       </x:c>
       <x:c r="D170" s="3" t="n">
         <x:v>28020</x:v>
@@ -3954,15 +3268,11 @@
       <x:c r="A171" s="2" t="n">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="B171" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">四象寒冰阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C171" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13105;7005;4005;3005</x:t>
-        </x:is>
+      <x:c r="B171" s="2" t="str">
+        <x:v>四象寒冰阵</x:v>
+      </x:c>
+      <x:c r="C171" s="3" t="str">
+        <x:v>13105;7005;4005;3005</x:v>
       </x:c>
       <x:c r="D171" s="3" t="n">
         <x:v>28021</x:v>
@@ -3975,15 +3285,11 @@
       <x:c r="A172" s="2" t="n">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="B172" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">烈焰困阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C172" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13106;7006;4006;3006</x:t>
-        </x:is>
+      <x:c r="B172" s="2" t="str">
+        <x:v>烈焰困阵</x:v>
+      </x:c>
+      <x:c r="C172" s="3" t="str">
+        <x:v>13106;7006;4006;3006</x:v>
       </x:c>
       <x:c r="D172" s="3" t="n">
         <x:v>28022</x:v>
@@ -3996,15 +3302,11 @@
       <x:c r="A173" s="2" t="n">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="B173" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">厚土御阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C173" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13107;7007;4007;3007</x:t>
-        </x:is>
+      <x:c r="B173" s="2" t="str">
+        <x:v>厚土御阵</x:v>
+      </x:c>
+      <x:c r="C173" s="3" t="str">
+        <x:v>13107;7007;4007;3007</x:v>
       </x:c>
       <x:c r="D173" s="3" t="n">
         <x:v>28023</x:v>
@@ -4017,15 +3319,11 @@
       <x:c r="A174" s="2" t="n">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="B174" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">五雷诛邪阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C174" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13108;7008;4008;3008</x:t>
-        </x:is>
+      <x:c r="B174" s="2" t="str">
+        <x:v>五雷诛邪阵</x:v>
+      </x:c>
+      <x:c r="C174" s="3" t="str">
+        <x:v>13108;7008;4008;3008</x:v>
       </x:c>
       <x:c r="D174" s="3" t="n">
         <x:v>28024</x:v>
@@ -4038,15 +3336,11 @@
       <x:c r="A175" s="2" t="n">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="B175" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地脉龙吟阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C175" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13109;7009;4009;3009</x:t>
-        </x:is>
+      <x:c r="B175" s="2" t="str">
+        <x:v>地脉龙吟阵</x:v>
+      </x:c>
+      <x:c r="C175" s="3" t="str">
+        <x:v>13109;7009;4009;3009</x:v>
       </x:c>
       <x:c r="D175" s="3" t="n">
         <x:v>28025</x:v>
@@ -4059,15 +3353,11 @@
       <x:c r="A176" s="2" t="n">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="B176" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星罗迷阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C176" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13110;7010;4010;3010</x:t>
-        </x:is>
+      <x:c r="B176" s="2" t="str">
+        <x:v>星罗迷阵</x:v>
+      </x:c>
+      <x:c r="C176" s="3" t="str">
+        <x:v>13110;7010;4010;3010</x:v>
       </x:c>
       <x:c r="D176" s="3" t="n">
         <x:v>28026</x:v>
@@ -4080,15 +3370,11 @@
       <x:c r="A177" s="2" t="n">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="B177" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九幻迷心阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C177" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13111;7011;4011;3011</x:t>
-        </x:is>
+      <x:c r="B177" s="2" t="str">
+        <x:v>九幻迷心阵</x:v>
+      </x:c>
+      <x:c r="C177" s="3" t="str">
+        <x:v>13111;7011;4011;3011</x:v>
       </x:c>
       <x:c r="D177" s="3" t="n">
         <x:v>28027</x:v>
@@ -4101,15 +3387,11 @@
       <x:c r="A178" s="2" t="n">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="B178" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九命续生阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C178" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13112;7012;4012;9012</x:t>
-        </x:is>
+      <x:c r="B178" s="2" t="str">
+        <x:v>九命续生阵</x:v>
+      </x:c>
+      <x:c r="C178" s="3" t="str">
+        <x:v>13112;7012;4012;9012</x:v>
       </x:c>
       <x:c r="D178" s="3" t="n">
         <x:v>28028</x:v>
@@ -4122,15 +3404,11 @@
       <x:c r="A179" s="2" t="n">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="B179" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">瑞兽祥云阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C179" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13113;7013;4013;3013</x:t>
-        </x:is>
+      <x:c r="B179" s="2" t="str">
+        <x:v>瑞兽祥云阵</x:v>
+      </x:c>
+      <x:c r="C179" s="3" t="str">
+        <x:v>13113;7013;4013;3013</x:v>
       </x:c>
       <x:c r="D179" s="3" t="n">
         <x:v>28029</x:v>
@@ -4143,15 +3421,11 @@
       <x:c r="A180" s="2" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="B180" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">真龙御天阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C180" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13114;7014;4014;3014</x:t>
-        </x:is>
+      <x:c r="B180" s="2" t="str">
+        <x:v>真龙御天阵</x:v>
+      </x:c>
+      <x:c r="C180" s="3" t="str">
+        <x:v>13114;7014;4014;3014</x:v>
       </x:c>
       <x:c r="D180" s="3" t="n">
         <x:v>28030</x:v>
@@ -4164,15 +3438,11 @@
       <x:c r="A181" s="2" t="n">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="B181" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凤舞涅槃阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C181" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13115;7015;4015;3015</x:t>
-        </x:is>
+      <x:c r="B181" s="2" t="str">
+        <x:v>凤舞涅槃阵</x:v>
+      </x:c>
+      <x:c r="C181" s="3" t="str">
+        <x:v>13115;7015;4015;3015</x:v>
       </x:c>
       <x:c r="D181" s="3" t="n">
         <x:v>28031</x:v>
@@ -4185,15 +3455,11 @@
       <x:c r="A182" s="2" t="n">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="B182" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌归一阵</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C182" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">13116;7016;4016;3016</x:t>
-        </x:is>
+      <x:c r="B182" s="2" t="str">
+        <x:v>混沌归一阵</x:v>
+      </x:c>
+      <x:c r="C182" s="3" t="str">
+        <x:v>13116;7016;4016;3016</x:v>
       </x:c>
       <x:c r="D182" s="3" t="n">
         <x:v>28032</x:v>
@@ -4206,15 +3472,11 @@
       <x:c r="A183" s="2" t="n">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="B183" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">驱兽符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C183" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7001;8001;9001</x:t>
-        </x:is>
+      <x:c r="B183" s="2" t="str">
+        <x:v>驱兽符</x:v>
+      </x:c>
+      <x:c r="C183" s="3" t="str">
+        <x:v>7001;8001;9001</x:v>
       </x:c>
       <x:c r="D183" s="3" t="n">
         <x:v>28033</x:v>
@@ -4227,15 +3489,11 @@
       <x:c r="A184" s="2" t="n">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="B184" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">避尘符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C184" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7002;8002;9001</x:t>
-        </x:is>
+      <x:c r="B184" s="2" t="str">
+        <x:v>避尘符</x:v>
+      </x:c>
+      <x:c r="C184" s="3" t="str">
+        <x:v>7002;8002;9001</x:v>
       </x:c>
       <x:c r="D184" s="3" t="n">
         <x:v>28034</x:v>
@@ -4248,15 +3506,11 @@
       <x:c r="A185" s="2" t="n">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="B185" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">火弹符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C185" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7003;8003;9002;3002</x:t>
-        </x:is>
+      <x:c r="B185" s="2" t="str">
+        <x:v>火弹符</x:v>
+      </x:c>
+      <x:c r="C185" s="3" t="str">
+        <x:v>7003;8003;9002;3002</x:v>
       </x:c>
       <x:c r="D185" s="3" t="n">
         <x:v>28035</x:v>
@@ -4269,15 +3523,11 @@
       <x:c r="A186" s="2" t="n">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="B186" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">金甲符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C186" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7004;8004;9002;3004</x:t>
-        </x:is>
+      <x:c r="B186" s="2" t="str">
+        <x:v>金甲符</x:v>
+      </x:c>
+      <x:c r="C186" s="3" t="str">
+        <x:v>7004;8004;9002;3004</x:v>
       </x:c>
       <x:c r="D186" s="3" t="n">
         <x:v>28036</x:v>
@@ -4290,15 +3540,11 @@
       <x:c r="A187" s="2" t="n">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="B187" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">冰锥符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C187" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7005;8005;9003;3005</x:t>
-        </x:is>
+      <x:c r="B187" s="2" t="str">
+        <x:v>冰锥符</x:v>
+      </x:c>
+      <x:c r="C187" s="3" t="str">
+        <x:v>7005;8005;9003;3005</x:v>
       </x:c>
       <x:c r="D187" s="3" t="n">
         <x:v>28037</x:v>
@@ -4311,15 +3557,11 @@
       <x:c r="A188" s="2" t="n">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="B188" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">炎爆符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C188" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7006;8006;9003;3006</x:t>
-        </x:is>
+      <x:c r="B188" s="2" t="str">
+        <x:v>炎爆符</x:v>
+      </x:c>
+      <x:c r="C188" s="3" t="str">
+        <x:v>7006;8006;9003;3006</x:v>
       </x:c>
       <x:c r="D188" s="3" t="n">
         <x:v>28038</x:v>
@@ -4332,15 +3574,11 @@
       <x:c r="A189" s="2" t="n">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="B189" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">青藤符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C189" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7007;8007;9004;3007</x:t>
-        </x:is>
+      <x:c r="B189" s="2" t="str">
+        <x:v>青藤符</x:v>
+      </x:c>
+      <x:c r="C189" s="3" t="str">
+        <x:v>7007;8007;9004;3007</x:v>
       </x:c>
       <x:c r="D189" s="3" t="n">
         <x:v>28039</x:v>
@@ -4353,15 +3591,11 @@
       <x:c r="A190" s="2" t="n">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="B190" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">五雷符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C190" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7008;8008;9004;3008</x:t>
-        </x:is>
+      <x:c r="B190" s="2" t="str">
+        <x:v>五雷符</x:v>
+      </x:c>
+      <x:c r="C190" s="3" t="str">
+        <x:v>7008;8008;9004;3008</x:v>
       </x:c>
       <x:c r="D190" s="3" t="n">
         <x:v>28040</x:v>
@@ -4374,15 +3608,11 @@
       <x:c r="A191" s="2" t="n">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="B191" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地裂符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C191" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7009;8009;9005;3009</x:t>
-        </x:is>
+      <x:c r="B191" s="2" t="str">
+        <x:v>地裂符</x:v>
+      </x:c>
+      <x:c r="C191" s="3" t="str">
+        <x:v>7009;8009;9005;3009</x:v>
       </x:c>
       <x:c r="D191" s="3" t="n">
         <x:v>28041</x:v>
@@ -4395,15 +3625,11 @@
       <x:c r="A192" s="2" t="n">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="B192" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星遁符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C192" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7010;8010;9005;3010</x:t>
-        </x:is>
+      <x:c r="B192" s="2" t="str">
+        <x:v>星遁符</x:v>
+      </x:c>
+      <x:c r="C192" s="3" t="str">
+        <x:v>7010;8010;9005;3010</x:v>
       </x:c>
       <x:c r="D192" s="3" t="n">
         <x:v>28042</x:v>
@@ -4416,15 +3642,11 @@
       <x:c r="A193" s="2" t="n">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="B193" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">幻身符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C193" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7011;8011;9006;3011</x:t>
-        </x:is>
+      <x:c r="B193" s="2" t="str">
+        <x:v>幻身符</x:v>
+      </x:c>
+      <x:c r="C193" s="3" t="str">
+        <x:v>7011;8011;9006;3011</x:v>
       </x:c>
       <x:c r="D193" s="3" t="n">
         <x:v>28043</x:v>
@@ -4437,15 +3659,11 @@
       <x:c r="A194" s="2" t="n">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="B194" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">续命符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C194" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7012;8012;9006;9012</x:t>
-        </x:is>
+      <x:c r="B194" s="2" t="str">
+        <x:v>续命符</x:v>
+      </x:c>
+      <x:c r="C194" s="3" t="str">
+        <x:v>7012;8012;9006;9012</x:v>
       </x:c>
       <x:c r="D194" s="3" t="n">
         <x:v>28044</x:v>
@@ -4458,15 +3676,11 @@
       <x:c r="A195" s="2" t="n">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="B195" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">祥瑞符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C195" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7013;8013;9007;3013</x:t>
-        </x:is>
+      <x:c r="B195" s="2" t="str">
+        <x:v>祥瑞符</x:v>
+      </x:c>
+      <x:c r="C195" s="3" t="str">
+        <x:v>7013;8013;9007;3013</x:v>
       </x:c>
       <x:c r="D195" s="3" t="n">
         <x:v>28045</x:v>
@@ -4479,15 +3693,11 @@
       <x:c r="A196" s="2" t="n">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="B196" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龙威符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C196" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7014;8014;9007;3014</x:t>
-        </x:is>
+      <x:c r="B196" s="2" t="str">
+        <x:v>龙威符</x:v>
+      </x:c>
+      <x:c r="C196" s="3" t="str">
+        <x:v>7014;8014;9007;3014</x:v>
       </x:c>
       <x:c r="D196" s="3" t="n">
         <x:v>28046</x:v>
@@ -4500,15 +3710,11 @@
       <x:c r="A197" s="2" t="n">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="B197" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">涅槃符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C197" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7015;8015;9008;3015</x:t>
-        </x:is>
+      <x:c r="B197" s="2" t="str">
+        <x:v>涅槃符</x:v>
+      </x:c>
+      <x:c r="C197" s="3" t="str">
+        <x:v>7015;8015;9008;3015</x:v>
       </x:c>
       <x:c r="D197" s="3" t="n">
         <x:v>28047</x:v>
@@ -4521,15 +3727,11 @@
       <x:c r="A198" s="2" t="n">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="B198" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">混沌符</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C198" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7016;8016;9008;3016</x:t>
-        </x:is>
+      <x:c r="B198" s="2" t="str">
+        <x:v>混沌符</x:v>
+      </x:c>
+      <x:c r="C198" s="3" t="str">
+        <x:v>7016;8016;9008;3016</x:v>
       </x:c>
       <x:c r="D198" s="3" t="n">
         <x:v>28048</x:v>
@@ -4542,15 +3744,11 @@
       <x:c r="A199" s="2" t="n">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="B199" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">引气筑基散</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C199" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1002;5002;9002</x:t>
-        </x:is>
+      <x:c r="B199" s="2" t="str">
+        <x:v>引气筑基散</x:v>
+      </x:c>
+      <x:c r="C199" s="3" t="str">
+        <x:v>1002;5002;9002</x:v>
       </x:c>
       <x:c r="D199" s="3" t="n">
         <x:v>28049</x:v>
@@ -4563,15 +3761,11 @@
       <x:c r="A200" s="2" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="B200" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凝元破境丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C200" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1003;5004;9004;3004</x:t>
-        </x:is>
+      <x:c r="B200" s="2" t="str">
+        <x:v>凝元破境丹</x:v>
+      </x:c>
+      <x:c r="C200" s="3" t="str">
+        <x:v>1003;5004;9004;3004</x:v>
       </x:c>
       <x:c r="D200" s="3" t="n">
         <x:v>28050</x:v>
@@ -4584,15 +3778,11 @@
       <x:c r="A201" s="2" t="n">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="B201" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">筑基破障丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C201" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1004;1005;27004;4004</x:t>
-        </x:is>
+      <x:c r="B201" s="2" t="str">
+        <x:v>筑基破障丹</x:v>
+      </x:c>
+      <x:c r="C201" s="3" t="str">
+        <x:v>1004;1005;27004;4004</x:v>
       </x:c>
       <x:c r="D201" s="3" t="n">
         <x:v>28051</x:v>
@@ -4605,15 +3795,11 @@
       <x:c r="A202" s="2" t="n">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="B202" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">固基培元丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C202" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1005;1006;9006;4006</x:t>
-        </x:is>
+      <x:c r="B202" s="2" t="str">
+        <x:v>固基培元丹</x:v>
+      </x:c>
+      <x:c r="C202" s="3" t="str">
+        <x:v>1005;1006;9006;4006</x:v>
       </x:c>
       <x:c r="D202" s="3" t="n">
         <x:v>28052</x:v>
@@ -4626,15 +3812,11 @@
       <x:c r="A203" s="2" t="n">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="B203" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">通玄化灵丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C203" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1007;1008;9008;4008</x:t>
-        </x:is>
+      <x:c r="B203" s="2" t="str">
+        <x:v>通玄化灵丹</x:v>
+      </x:c>
+      <x:c r="C203" s="3" t="str">
+        <x:v>1007;1008;9008;4008</x:v>
       </x:c>
       <x:c r="D203" s="3" t="n">
         <x:v>28053</x:v>
@@ -4647,15 +3829,11 @@
       <x:c r="A204" s="2" t="n">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="B204" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">金丹破障丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C204" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1009;1010;27007;4009</x:t>
-        </x:is>
+      <x:c r="B204" s="2" t="str">
+        <x:v>金丹破障丹</x:v>
+      </x:c>
+      <x:c r="C204" s="3" t="str">
+        <x:v>1009;1010;27007;4009</x:v>
       </x:c>
       <x:c r="D204" s="3" t="n">
         <x:v>28054</x:v>
@@ -4668,15 +3846,11 @@
       <x:c r="A205" s="2" t="n">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="B205" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">凝丹化形丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C205" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1009;1011;9011;4011</x:t>
-        </x:is>
+      <x:c r="B205" s="2" t="str">
+        <x:v>凝丹化形丹</x:v>
+      </x:c>
+      <x:c r="C205" s="3" t="str">
+        <x:v>1009;1011;9011;4011</x:v>
       </x:c>
       <x:c r="D205" s="3" t="n">
         <x:v>28055</x:v>
@@ -4689,15 +3863,11 @@
       <x:c r="A206" s="2" t="n">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="B206" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">九转金丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C206" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1012;1011;9012;4012</x:t>
-        </x:is>
+      <x:c r="B206" s="2" t="str">
+        <x:v>九转金丹</x:v>
+      </x:c>
+      <x:c r="C206" s="3" t="str">
+        <x:v>1012;1011;9012;4012</x:v>
       </x:c>
       <x:c r="D206" s="3" t="n">
         <x:v>28056</x:v>
@@ -4710,15 +3880,11 @@
       <x:c r="A207" s="2" t="n">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="B207" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">元婴破障丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C207" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1012;2009;27009;8012</x:t>
-        </x:is>
+      <x:c r="B207" s="2" t="str">
+        <x:v>元婴破障丹</x:v>
+      </x:c>
+      <x:c r="C207" s="3" t="str">
+        <x:v>1012;2009;27009;8012</x:v>
       </x:c>
       <x:c r="D207" s="3" t="n">
         <x:v>28057</x:v>
@@ -4731,15 +3897,11 @@
       <x:c r="A208" s="2" t="n">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="B208" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">元婴凝神丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C208" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7013;7014;9013;4013</x:t>
-        </x:is>
+      <x:c r="B208" s="2" t="str">
+        <x:v>元婴凝神丹</x:v>
+      </x:c>
+      <x:c r="C208" s="3" t="str">
+        <x:v>7013;7014;9013;4013</x:v>
       </x:c>
       <x:c r="D208" s="3" t="n">
         <x:v>28058</x:v>
@@ -4752,15 +3914,11 @@
       <x:c r="A209" s="2" t="n">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="B209" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">元婴归元丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C209" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7015;7014;9015;4014</x:t>
-        </x:is>
+      <x:c r="B209" s="2" t="str">
+        <x:v>元婴归元丹</x:v>
+      </x:c>
+      <x:c r="C209" s="3" t="str">
+        <x:v>7015;7014;9015;4014</x:v>
       </x:c>
       <x:c r="D209" s="3" t="n">
         <x:v>28059</x:v>
@@ -4773,15 +3931,11 @@
       <x:c r="A210" s="2" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="B210" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">化神渡劫丹</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C210" s="3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">7016;8016;3016;4016</x:t>
-        </x:is>
+      <x:c r="B210" s="2" t="str">
+        <x:v>化神渡劫丹</x:v>
+      </x:c>
+      <x:c r="C210" s="3" t="str">
+        <x:v>7016;8016;3016;4016</x:v>
       </x:c>
       <x:c r="D210" s="3" t="n">
         <x:v>28060</x:v>
